--- a/docs/wbs/(아이뱅크) TOPIK_Myanmar_WBS 세부 개발 일정_v1.2.xlsx
+++ b/docs/wbs/(아이뱅크) TOPIK_Myanmar_WBS 세부 개발 일정_v1.2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jhcho/Documents/Myanmar/wbs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jhcho/Documents/Myanmar_v2.0/docs/wbs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9E1F4F-CAAE-1E4B-96D9-359BB6FD191D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A7DA04-21D0-AA45-9506-511C1C7B04B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9840" yWindow="-21000" windowWidth="38400" windowHeight="19320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3421,6 +3421,77 @@
     <xf numFmtId="178" fontId="11" fillId="14" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="106" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="94" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="108" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -3430,38 +3501,11 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3478,7 +3522,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3489,60 +3532,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="94" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="106" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="108" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4150,7 +4150,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="12" customHeight="1" thickBot="1">
-      <c r="A1" s="208"/>
+      <c r="A1" s="234"/>
       <c r="B1" s="1"/>
       <c r="C1" s="119"/>
       <c r="D1" s="91"/>
@@ -4204,43 +4204,43 @@
       <c r="AZ1" s="9"/>
     </row>
     <row r="2" spans="1:52" ht="18.75" customHeight="1" outlineLevel="1" thickTop="1">
-      <c r="A2" s="209"/>
-      <c r="B2" s="216" t="s">
+      <c r="A2" s="235"/>
+      <c r="B2" s="240" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="217"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="218"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
       <c r="H2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="236" t="s">
+      <c r="I2" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="237"/>
+      <c r="J2" s="206"/>
       <c r="K2" s="11"/>
       <c r="L2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="220" t="s">
+      <c r="M2" s="244" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="221"/>
-      <c r="O2" s="221"/>
-      <c r="P2" s="222"/>
-      <c r="Q2" s="226" t="s">
+      <c r="N2" s="213"/>
+      <c r="O2" s="213"/>
+      <c r="P2" s="245"/>
+      <c r="Q2" s="249" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="221"/>
-      <c r="S2" s="221"/>
-      <c r="T2" s="227"/>
-      <c r="U2" s="241" t="s">
+      <c r="R2" s="213"/>
+      <c r="S2" s="213"/>
+      <c r="T2" s="250"/>
+      <c r="U2" s="212" t="s">
         <v>6</v>
       </c>
-      <c r="V2" s="221"/>
-      <c r="W2" s="221"/>
-      <c r="X2" s="242"/>
+      <c r="V2" s="213"/>
+      <c r="W2" s="213"/>
+      <c r="X2" s="214"/>
       <c r="Y2" s="13"/>
       <c r="Z2" s="14"/>
       <c r="AA2" s="14"/>
@@ -4271,15 +4271,15 @@
       <c r="AZ2" s="9"/>
     </row>
     <row r="3" spans="1:52" ht="18.75" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="A3" s="210"/>
-      <c r="B3" s="219"/>
-      <c r="C3" s="217"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
-      <c r="H3" s="213" t="e">
-        <f>M6*J3+#REF!*J4+#REF!*J5</f>
-        <v>#REF!</v>
+      <c r="A3" s="236"/>
+      <c r="B3" s="243"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="H3" s="237">
+        <f>M6*J3+Q6*J4+U6*J5</f>
+        <v>0.99928571428571433</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>4</v>
@@ -4291,27 +4291,27 @@
       <c r="L3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="246">
+      <c r="M3" s="220">
         <f>COUNTA(N13:N150)</f>
         <v>138</v>
       </c>
-      <c r="N3" s="201"/>
-      <c r="O3" s="201"/>
-      <c r="P3" s="212"/>
-      <c r="Q3" s="246">
+      <c r="N3" s="199"/>
+      <c r="O3" s="199"/>
+      <c r="P3" s="200"/>
+      <c r="Q3" s="220">
         <f>COUNTA(R13:R150)</f>
         <v>138</v>
       </c>
-      <c r="R3" s="201"/>
-      <c r="S3" s="201"/>
-      <c r="T3" s="212"/>
-      <c r="U3" s="203">
-        <f>COUNTA(V13:V150)</f>
-        <v>138</v>
-      </c>
-      <c r="V3" s="201"/>
-      <c r="W3" s="201"/>
-      <c r="X3" s="204"/>
+      <c r="R3" s="199"/>
+      <c r="S3" s="199"/>
+      <c r="T3" s="200"/>
+      <c r="U3" s="228">
+        <f>COUNTA(V13:V152)</f>
+        <v>140</v>
+      </c>
+      <c r="V3" s="199"/>
+      <c r="W3" s="199"/>
+      <c r="X3" s="222"/>
       <c r="Y3" s="19"/>
       <c r="Z3" s="14"/>
       <c r="AA3" s="14"/>
@@ -4343,12 +4343,12 @@
     </row>
     <row r="4" spans="1:52" ht="18.75" customHeight="1" outlineLevel="1" thickTop="1">
       <c r="A4" s="20"/>
-      <c r="B4" s="219"/>
-      <c r="C4" s="217"/>
-      <c r="D4" s="218"/>
-      <c r="E4" s="218"/>
-      <c r="F4" s="218"/>
-      <c r="H4" s="214"/>
+      <c r="B4" s="243"/>
+      <c r="C4" s="241"/>
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="H4" s="238"/>
       <c r="I4" s="21" t="s">
         <v>5</v>
       </c>
@@ -4359,27 +4359,27 @@
       <c r="L4" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="211">
+      <c r="M4" s="198">
         <f>M3-M5</f>
-        <v>138</v>
-      </c>
-      <c r="N4" s="201"/>
-      <c r="O4" s="201"/>
-      <c r="P4" s="212"/>
-      <c r="Q4" s="211">
+        <v>0</v>
+      </c>
+      <c r="N4" s="199"/>
+      <c r="O4" s="199"/>
+      <c r="P4" s="200"/>
+      <c r="Q4" s="198">
         <f>Q3-Q5</f>
-        <v>138</v>
-      </c>
-      <c r="R4" s="201"/>
-      <c r="S4" s="201"/>
-      <c r="T4" s="212"/>
-      <c r="U4" s="247">
+        <v>0</v>
+      </c>
+      <c r="R4" s="199"/>
+      <c r="S4" s="199"/>
+      <c r="T4" s="200"/>
+      <c r="U4" s="221">
         <f>U3-U5</f>
-        <v>138</v>
-      </c>
-      <c r="V4" s="201"/>
-      <c r="W4" s="201"/>
-      <c r="X4" s="204"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="199"/>
+      <c r="W4" s="199"/>
+      <c r="X4" s="222"/>
       <c r="Y4" s="19"/>
       <c r="Z4" s="14"/>
       <c r="AA4" s="14"/>
@@ -4417,7 +4417,7 @@
       <c r="E5" s="92"/>
       <c r="F5" s="92"/>
       <c r="G5" s="24"/>
-      <c r="H5" s="214"/>
+      <c r="H5" s="238"/>
       <c r="I5" s="21" t="s">
         <v>6</v>
       </c>
@@ -4428,27 +4428,27 @@
       <c r="L5" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="211">
+      <c r="M5" s="198">
         <f>COUNTIF(N13:N150, "100%")</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="201"/>
-      <c r="O5" s="201"/>
-      <c r="P5" s="212"/>
-      <c r="Q5" s="211">
+        <v>138</v>
+      </c>
+      <c r="N5" s="199"/>
+      <c r="O5" s="199"/>
+      <c r="P5" s="200"/>
+      <c r="Q5" s="198">
         <f>COUNTIF(R13:R150, "100%")</f>
-        <v>0</v>
-      </c>
-      <c r="R5" s="201"/>
-      <c r="S5" s="201"/>
-      <c r="T5" s="212"/>
-      <c r="U5" s="247">
-        <f>COUNTIF(V13:V150, "100%")</f>
-        <v>0</v>
-      </c>
-      <c r="V5" s="201"/>
-      <c r="W5" s="201"/>
-      <c r="X5" s="204"/>
+        <v>138</v>
+      </c>
+      <c r="R5" s="199"/>
+      <c r="S5" s="199"/>
+      <c r="T5" s="200"/>
+      <c r="U5" s="221">
+        <f>COUNTIF(V13:V152, "100%")</f>
+        <v>139</v>
+      </c>
+      <c r="V5" s="199"/>
+      <c r="W5" s="199"/>
+      <c r="X5" s="222"/>
       <c r="Y5" s="27"/>
       <c r="Z5" s="28" t="s">
         <v>10</v>
@@ -4496,34 +4496,34 @@
       <c r="E6" s="92"/>
       <c r="F6" s="97"/>
       <c r="G6" s="33"/>
-      <c r="H6" s="215"/>
+      <c r="H6" s="239"/>
       <c r="I6" s="34"/>
       <c r="J6" s="35"/>
       <c r="K6" s="25"/>
       <c r="L6" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="205">
+      <c r="M6" s="229">
         <f>IFERROR(M5/M3, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="206"/>
-      <c r="O6" s="206"/>
-      <c r="P6" s="207"/>
-      <c r="Q6" s="205">
+        <v>1</v>
+      </c>
+      <c r="N6" s="224"/>
+      <c r="O6" s="224"/>
+      <c r="P6" s="230"/>
+      <c r="Q6" s="229">
         <f>IFERROR(Q5/Q3, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="R6" s="206"/>
-      <c r="S6" s="206"/>
-      <c r="T6" s="207"/>
-      <c r="U6" s="248">
+        <v>1</v>
+      </c>
+      <c r="R6" s="224"/>
+      <c r="S6" s="224"/>
+      <c r="T6" s="230"/>
+      <c r="U6" s="223">
         <f>IFERROR(U5/U3, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V6" s="206"/>
-      <c r="W6" s="206"/>
-      <c r="X6" s="249"/>
+        <v>0.99285714285714288</v>
+      </c>
+      <c r="V6" s="224"/>
+      <c r="W6" s="224"/>
+      <c r="X6" s="225"/>
       <c r="Y6" s="37"/>
       <c r="Z6" s="38"/>
       <c r="AA6" s="39"/>
@@ -4611,73 +4611,73 @@
     </row>
     <row r="8" spans="1:52" ht="16" customHeight="1" thickTop="1" thickBot="1">
       <c r="A8" s="51"/>
-      <c r="B8" s="239" t="s">
+      <c r="B8" s="210" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="228" t="s">
+      <c r="C8" s="215" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="228" t="s">
+      <c r="D8" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="228" t="s">
+      <c r="E8" s="215" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="228" t="s">
+      <c r="F8" s="215" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="228" t="s">
+      <c r="G8" s="215" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="228" t="s">
+      <c r="H8" s="215" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="251" t="s">
+      <c r="I8" s="201" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="234"/>
-      <c r="K8" s="234"/>
-      <c r="L8" s="234"/>
-      <c r="M8" s="243" t="s">
+      <c r="J8" s="196"/>
+      <c r="K8" s="196"/>
+      <c r="L8" s="196"/>
+      <c r="M8" s="217" t="s">
         <v>4</v>
       </c>
-      <c r="N8" s="244"/>
-      <c r="O8" s="244"/>
-      <c r="P8" s="245"/>
-      <c r="Q8" s="230" t="s">
+      <c r="N8" s="218"/>
+      <c r="O8" s="218"/>
+      <c r="P8" s="219"/>
+      <c r="Q8" s="251" t="s">
         <v>5</v>
       </c>
-      <c r="R8" s="231"/>
-      <c r="S8" s="231"/>
-      <c r="T8" s="232"/>
-      <c r="U8" s="238" t="s">
+      <c r="R8" s="208"/>
+      <c r="S8" s="208"/>
+      <c r="T8" s="209"/>
+      <c r="U8" s="207" t="s">
         <v>6</v>
       </c>
-      <c r="V8" s="231"/>
-      <c r="W8" s="231"/>
-      <c r="X8" s="232"/>
+      <c r="V8" s="208"/>
+      <c r="W8" s="208"/>
+      <c r="X8" s="209"/>
       <c r="Y8" s="52"/>
-      <c r="Z8" s="233" t="s">
+      <c r="Z8" s="204" t="s">
         <v>22</v>
       </c>
-      <c r="AA8" s="234"/>
-      <c r="AB8" s="234"/>
-      <c r="AC8" s="234"/>
-      <c r="AD8" s="235"/>
-      <c r="AE8" s="250" t="s">
+      <c r="AA8" s="196"/>
+      <c r="AB8" s="196"/>
+      <c r="AC8" s="196"/>
+      <c r="AD8" s="197"/>
+      <c r="AE8" s="195" t="s">
         <v>23</v>
       </c>
-      <c r="AF8" s="234"/>
-      <c r="AG8" s="234"/>
-      <c r="AH8" s="234"/>
-      <c r="AI8" s="235"/>
-      <c r="AJ8" s="250" t="s">
+      <c r="AF8" s="196"/>
+      <c r="AG8" s="196"/>
+      <c r="AH8" s="196"/>
+      <c r="AI8" s="197"/>
+      <c r="AJ8" s="195" t="s">
         <v>24</v>
       </c>
-      <c r="AK8" s="234"/>
-      <c r="AL8" s="234"/>
-      <c r="AM8" s="234"/>
-      <c r="AN8" s="235"/>
+      <c r="AK8" s="196"/>
+      <c r="AL8" s="196"/>
+      <c r="AM8" s="196"/>
+      <c r="AN8" s="197"/>
       <c r="AO8" s="9"/>
       <c r="AP8" s="9"/>
       <c r="AQ8" s="9"/>
@@ -4693,17 +4693,17 @@
     </row>
     <row r="9" spans="1:52" ht="29" customHeight="1" thickBot="1">
       <c r="A9" s="53"/>
-      <c r="B9" s="240"/>
-      <c r="C9" s="229"/>
-      <c r="D9" s="229"/>
-      <c r="E9" s="229"/>
-      <c r="F9" s="229"/>
-      <c r="G9" s="229"/>
-      <c r="H9" s="229"/>
-      <c r="I9" s="252"/>
-      <c r="J9" s="253"/>
-      <c r="K9" s="253"/>
-      <c r="L9" s="253"/>
+      <c r="B9" s="211"/>
+      <c r="C9" s="216"/>
+      <c r="D9" s="216"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="216"/>
+      <c r="H9" s="216"/>
+      <c r="I9" s="202"/>
+      <c r="J9" s="203"/>
+      <c r="K9" s="203"/>
+      <c r="L9" s="203"/>
       <c r="M9" s="82" t="s">
         <v>25</v>
       </c>
@@ -4812,15 +4812,15 @@
       <c r="H10" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="223"/>
-      <c r="J10" s="224"/>
-      <c r="K10" s="224"/>
-      <c r="L10" s="225"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="247"/>
+      <c r="K10" s="247"/>
+      <c r="L10" s="248"/>
       <c r="M10" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N10" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="85">
         <v>46146</v>
@@ -4878,15 +4878,15 @@
       <c r="H11" s="107" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="200"/>
-      <c r="J11" s="201"/>
-      <c r="K11" s="201"/>
-      <c r="L11" s="202"/>
+      <c r="I11" s="226"/>
+      <c r="J11" s="199"/>
+      <c r="K11" s="199"/>
+      <c r="L11" s="227"/>
       <c r="M11" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N11" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="85">
         <v>46146</v>
@@ -4944,15 +4944,15 @@
       <c r="H12" s="107" t="s">
         <v>44</v>
       </c>
-      <c r="I12" s="200"/>
-      <c r="J12" s="201"/>
-      <c r="K12" s="201"/>
-      <c r="L12" s="202"/>
+      <c r="I12" s="226"/>
+      <c r="J12" s="199"/>
+      <c r="K12" s="199"/>
+      <c r="L12" s="227"/>
       <c r="M12" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N12" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="85">
         <v>46154</v>
@@ -5016,17 +5016,17 @@
       <c r="H13" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I13" s="194" t="s">
+      <c r="I13" s="231" t="s">
         <v>228</v>
       </c>
-      <c r="J13" s="195"/>
-      <c r="K13" s="195"/>
-      <c r="L13" s="196"/>
+      <c r="J13" s="232"/>
+      <c r="K13" s="232"/>
+      <c r="L13" s="233"/>
       <c r="M13" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N13" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="130">
         <v>46162</v>
@@ -5038,7 +5038,7 @@
         <v>247</v>
       </c>
       <c r="R13" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="130">
         <v>46174</v>
@@ -5050,7 +5050,7 @@
         <v>45</v>
       </c>
       <c r="V13" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="130">
         <v>46195</v>
@@ -5104,17 +5104,17 @@
       <c r="H14" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I14" s="194" t="s">
+      <c r="I14" s="231" t="s">
         <v>53</v>
       </c>
-      <c r="J14" s="195"/>
-      <c r="K14" s="195"/>
-      <c r="L14" s="196"/>
+      <c r="J14" s="232"/>
+      <c r="K14" s="232"/>
+      <c r="L14" s="233"/>
       <c r="M14" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N14" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="130">
         <v>46162</v>
@@ -5126,7 +5126,7 @@
         <v>247</v>
       </c>
       <c r="R14" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="130">
         <v>46174</v>
@@ -5138,7 +5138,7 @@
         <v>45</v>
       </c>
       <c r="V14" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="130">
         <v>46195</v>
@@ -5192,15 +5192,15 @@
       <c r="H15" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I15" s="194"/>
-      <c r="J15" s="195"/>
-      <c r="K15" s="195"/>
-      <c r="L15" s="196"/>
+      <c r="I15" s="231"/>
+      <c r="J15" s="232"/>
+      <c r="K15" s="232"/>
+      <c r="L15" s="233"/>
       <c r="M15" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N15" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="130">
         <v>46162</v>
@@ -5212,7 +5212,7 @@
         <v>247</v>
       </c>
       <c r="R15" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="130">
         <v>46174</v>
@@ -5224,7 +5224,7 @@
         <v>45</v>
       </c>
       <c r="V15" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="130">
         <v>46195</v>
@@ -5278,17 +5278,17 @@
       <c r="H16" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I16" s="194" t="s">
+      <c r="I16" s="231" t="s">
         <v>229</v>
       </c>
-      <c r="J16" s="195"/>
-      <c r="K16" s="195"/>
-      <c r="L16" s="196"/>
+      <c r="J16" s="232"/>
+      <c r="K16" s="232"/>
+      <c r="L16" s="233"/>
       <c r="M16" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N16" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="130">
         <v>46162</v>
@@ -5300,7 +5300,7 @@
         <v>247</v>
       </c>
       <c r="R16" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="130">
         <v>46174</v>
@@ -5312,7 +5312,7 @@
         <v>45</v>
       </c>
       <c r="V16" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="130">
         <v>46195</v>
@@ -5364,15 +5364,15 @@
       <c r="H17" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I17" s="194"/>
-      <c r="J17" s="195"/>
-      <c r="K17" s="195"/>
-      <c r="L17" s="196"/>
+      <c r="I17" s="231"/>
+      <c r="J17" s="232"/>
+      <c r="K17" s="232"/>
+      <c r="L17" s="233"/>
       <c r="M17" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N17" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="130">
         <v>46162</v>
@@ -5384,7 +5384,7 @@
         <v>247</v>
       </c>
       <c r="R17" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="130">
         <v>46174</v>
@@ -5396,7 +5396,7 @@
         <v>45</v>
       </c>
       <c r="V17" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="130">
         <v>46195</v>
@@ -5450,17 +5450,17 @@
       <c r="H18" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I18" s="194" t="s">
+      <c r="I18" s="231" t="s">
         <v>60</v>
       </c>
-      <c r="J18" s="195"/>
-      <c r="K18" s="195"/>
-      <c r="L18" s="196"/>
+      <c r="J18" s="232"/>
+      <c r="K18" s="232"/>
+      <c r="L18" s="233"/>
       <c r="M18" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N18" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="130">
         <v>46167</v>
@@ -5472,7 +5472,7 @@
         <v>247</v>
       </c>
       <c r="R18" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="130">
         <v>46174</v>
@@ -5484,7 +5484,7 @@
         <v>45</v>
       </c>
       <c r="V18" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="130">
         <v>46195</v>
@@ -5536,17 +5536,17 @@
       <c r="H19" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="194" t="s">
+      <c r="I19" s="231" t="s">
         <v>63</v>
       </c>
-      <c r="J19" s="195"/>
-      <c r="K19" s="195"/>
-      <c r="L19" s="196"/>
+      <c r="J19" s="232"/>
+      <c r="K19" s="232"/>
+      <c r="L19" s="233"/>
       <c r="M19" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N19" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="130">
         <v>46167</v>
@@ -5558,7 +5558,7 @@
         <v>247</v>
       </c>
       <c r="R19" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="130">
         <v>46174</v>
@@ -5570,7 +5570,7 @@
         <v>45</v>
       </c>
       <c r="V19" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="130">
         <v>46195</v>
@@ -5622,17 +5622,17 @@
       <c r="H20" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I20" s="194" t="s">
+      <c r="I20" s="231" t="s">
         <v>65</v>
       </c>
-      <c r="J20" s="195"/>
-      <c r="K20" s="195"/>
-      <c r="L20" s="196"/>
+      <c r="J20" s="232"/>
+      <c r="K20" s="232"/>
+      <c r="L20" s="233"/>
       <c r="M20" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N20" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="130">
         <v>46167</v>
@@ -5644,7 +5644,7 @@
         <v>247</v>
       </c>
       <c r="R20" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="130">
         <v>46174</v>
@@ -5656,7 +5656,7 @@
         <v>45</v>
       </c>
       <c r="V20" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="130">
         <v>46195</v>
@@ -5708,15 +5708,15 @@
       <c r="H21" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I21" s="194"/>
-      <c r="J21" s="195"/>
-      <c r="K21" s="195"/>
-      <c r="L21" s="196"/>
+      <c r="I21" s="231"/>
+      <c r="J21" s="232"/>
+      <c r="K21" s="232"/>
+      <c r="L21" s="233"/>
       <c r="M21" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N21" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="130">
         <v>46167</v>
@@ -5728,7 +5728,7 @@
         <v>247</v>
       </c>
       <c r="R21" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="130">
         <v>46174</v>
@@ -5740,7 +5740,7 @@
         <v>45</v>
       </c>
       <c r="V21" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="130">
         <v>46195</v>
@@ -5792,15 +5792,15 @@
       <c r="H22" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I22" s="194"/>
-      <c r="J22" s="195"/>
-      <c r="K22" s="195"/>
-      <c r="L22" s="196"/>
+      <c r="I22" s="231"/>
+      <c r="J22" s="232"/>
+      <c r="K22" s="232"/>
+      <c r="L22" s="233"/>
       <c r="M22" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N22" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="130">
         <v>46167</v>
@@ -5812,7 +5812,7 @@
         <v>247</v>
       </c>
       <c r="R22" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" s="130">
         <v>46174</v>
@@ -5824,7 +5824,7 @@
         <v>45</v>
       </c>
       <c r="V22" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="130">
         <v>46195</v>
@@ -5878,17 +5878,17 @@
       <c r="H23" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I23" s="194" t="s">
+      <c r="I23" s="231" t="s">
         <v>70</v>
       </c>
-      <c r="J23" s="195"/>
-      <c r="K23" s="195"/>
-      <c r="L23" s="196"/>
+      <c r="J23" s="232"/>
+      <c r="K23" s="232"/>
+      <c r="L23" s="233"/>
       <c r="M23" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N23" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="130">
         <v>46168</v>
@@ -5900,7 +5900,7 @@
         <v>247</v>
       </c>
       <c r="R23" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="130">
         <v>46181</v>
@@ -5912,7 +5912,7 @@
         <v>45</v>
       </c>
       <c r="V23" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="130">
         <v>46195</v>
@@ -5964,15 +5964,15 @@
       <c r="H24" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I24" s="194"/>
-      <c r="J24" s="195"/>
-      <c r="K24" s="195"/>
-      <c r="L24" s="196"/>
+      <c r="I24" s="231"/>
+      <c r="J24" s="232"/>
+      <c r="K24" s="232"/>
+      <c r="L24" s="233"/>
       <c r="M24" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N24" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="130">
         <v>46168</v>
@@ -5984,7 +5984,7 @@
         <v>247</v>
       </c>
       <c r="R24" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" s="130">
         <v>46181</v>
@@ -5996,7 +5996,7 @@
         <v>45</v>
       </c>
       <c r="V24" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="130">
         <v>46195</v>
@@ -6048,15 +6048,15 @@
       <c r="H25" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I25" s="194"/>
-      <c r="J25" s="195"/>
-      <c r="K25" s="195"/>
-      <c r="L25" s="196"/>
+      <c r="I25" s="231"/>
+      <c r="J25" s="232"/>
+      <c r="K25" s="232"/>
+      <c r="L25" s="233"/>
       <c r="M25" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N25" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="130">
         <v>46168</v>
@@ -6068,7 +6068,7 @@
         <v>247</v>
       </c>
       <c r="R25" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="130">
         <v>46181</v>
@@ -6080,7 +6080,7 @@
         <v>45</v>
       </c>
       <c r="V25" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="130">
         <v>46195</v>
@@ -6132,15 +6132,15 @@
       <c r="H26" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I26" s="194"/>
-      <c r="J26" s="195"/>
-      <c r="K26" s="195"/>
-      <c r="L26" s="196"/>
+      <c r="I26" s="231"/>
+      <c r="J26" s="232"/>
+      <c r="K26" s="232"/>
+      <c r="L26" s="233"/>
       <c r="M26" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N26" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="130">
         <v>46168</v>
@@ -6152,7 +6152,7 @@
         <v>247</v>
       </c>
       <c r="R26" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="130">
         <v>46181</v>
@@ -6164,7 +6164,7 @@
         <v>45</v>
       </c>
       <c r="V26" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="130">
         <v>46195</v>
@@ -6218,17 +6218,17 @@
       <c r="H27" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I27" s="194" t="s">
+      <c r="I27" s="231" t="s">
         <v>230</v>
       </c>
-      <c r="J27" s="195"/>
-      <c r="K27" s="195"/>
-      <c r="L27" s="196"/>
+      <c r="J27" s="232"/>
+      <c r="K27" s="232"/>
+      <c r="L27" s="233"/>
       <c r="M27" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N27" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="130">
         <v>46168</v>
@@ -6240,7 +6240,7 @@
         <v>247</v>
       </c>
       <c r="R27" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="130">
         <v>46181</v>
@@ -6252,7 +6252,7 @@
         <v>45</v>
       </c>
       <c r="V27" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="130">
         <v>46195</v>
@@ -6304,15 +6304,15 @@
       <c r="H28" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I28" s="194"/>
-      <c r="J28" s="195"/>
-      <c r="K28" s="195"/>
-      <c r="L28" s="196"/>
+      <c r="I28" s="231"/>
+      <c r="J28" s="232"/>
+      <c r="K28" s="232"/>
+      <c r="L28" s="233"/>
       <c r="M28" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N28" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="130">
         <v>46168</v>
@@ -6324,7 +6324,7 @@
         <v>247</v>
       </c>
       <c r="R28" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" s="130">
         <v>46181</v>
@@ -6336,7 +6336,7 @@
         <v>45</v>
       </c>
       <c r="V28" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" s="130">
         <v>46195</v>
@@ -6388,17 +6388,17 @@
       <c r="H29" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I29" s="194" t="s">
+      <c r="I29" s="231" t="s">
         <v>78</v>
       </c>
-      <c r="J29" s="195"/>
-      <c r="K29" s="195"/>
-      <c r="L29" s="196"/>
+      <c r="J29" s="232"/>
+      <c r="K29" s="232"/>
+      <c r="L29" s="233"/>
       <c r="M29" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N29" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="130">
         <v>46168</v>
@@ -6410,7 +6410,7 @@
         <v>247</v>
       </c>
       <c r="R29" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" s="130">
         <v>46181</v>
@@ -6422,7 +6422,7 @@
         <v>45</v>
       </c>
       <c r="V29" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="130">
         <v>46195</v>
@@ -6474,15 +6474,15 @@
       <c r="H30" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I30" s="194"/>
-      <c r="J30" s="195"/>
-      <c r="K30" s="195"/>
-      <c r="L30" s="196"/>
+      <c r="I30" s="231"/>
+      <c r="J30" s="232"/>
+      <c r="K30" s="232"/>
+      <c r="L30" s="233"/>
       <c r="M30" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N30" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="130">
         <v>46168</v>
@@ -6494,7 +6494,7 @@
         <v>247</v>
       </c>
       <c r="R30" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="130">
         <v>46181</v>
@@ -6506,7 +6506,7 @@
         <v>45</v>
       </c>
       <c r="V30" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="130">
         <v>46195</v>
@@ -6560,17 +6560,17 @@
       <c r="H31" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I31" s="194" t="s">
+      <c r="I31" s="231" t="s">
         <v>82</v>
       </c>
-      <c r="J31" s="195"/>
-      <c r="K31" s="195"/>
-      <c r="L31" s="196"/>
+      <c r="J31" s="232"/>
+      <c r="K31" s="232"/>
+      <c r="L31" s="233"/>
       <c r="M31" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N31" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="130">
         <v>46174</v>
@@ -6582,7 +6582,7 @@
         <v>247</v>
       </c>
       <c r="R31" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="130">
         <v>46181</v>
@@ -6594,7 +6594,7 @@
         <v>45</v>
       </c>
       <c r="V31" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="130">
         <v>46195</v>
@@ -6646,17 +6646,17 @@
       <c r="H32" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I32" s="194" t="s">
+      <c r="I32" s="231" t="s">
         <v>231</v>
       </c>
-      <c r="J32" s="195"/>
-      <c r="K32" s="195"/>
-      <c r="L32" s="196"/>
+      <c r="J32" s="232"/>
+      <c r="K32" s="232"/>
+      <c r="L32" s="233"/>
       <c r="M32" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N32" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="130">
         <v>46174</v>
@@ -6668,7 +6668,7 @@
         <v>247</v>
       </c>
       <c r="R32" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="130">
         <v>46181</v>
@@ -6680,7 +6680,7 @@
         <v>45</v>
       </c>
       <c r="V32" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="130">
         <v>46195</v>
@@ -6734,17 +6734,17 @@
       <c r="H33" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I33" s="194" t="s">
+      <c r="I33" s="231" t="s">
         <v>232</v>
       </c>
-      <c r="J33" s="195"/>
-      <c r="K33" s="195"/>
-      <c r="L33" s="196"/>
+      <c r="J33" s="232"/>
+      <c r="K33" s="232"/>
+      <c r="L33" s="233"/>
       <c r="M33" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N33" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="130">
         <v>46174</v>
@@ -6756,7 +6756,7 @@
         <v>247</v>
       </c>
       <c r="R33" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" s="130">
         <v>46181</v>
@@ -6768,7 +6768,7 @@
         <v>45</v>
       </c>
       <c r="V33" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="130">
         <v>46195</v>
@@ -6822,17 +6822,17 @@
       <c r="H34" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I34" s="194" t="s">
+      <c r="I34" s="231" t="s">
         <v>233</v>
       </c>
-      <c r="J34" s="195"/>
-      <c r="K34" s="195"/>
-      <c r="L34" s="196"/>
+      <c r="J34" s="232"/>
+      <c r="K34" s="232"/>
+      <c r="L34" s="233"/>
       <c r="M34" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N34" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="130">
         <v>46174</v>
@@ -6844,7 +6844,7 @@
         <v>247</v>
       </c>
       <c r="R34" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" s="130">
         <v>46181</v>
@@ -6856,7 +6856,7 @@
         <v>45</v>
       </c>
       <c r="V34" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="130">
         <v>46195</v>
@@ -6910,17 +6910,17 @@
       <c r="H35" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I35" s="194" t="s">
+      <c r="I35" s="231" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="195"/>
-      <c r="K35" s="195"/>
-      <c r="L35" s="196"/>
+      <c r="J35" s="232"/>
+      <c r="K35" s="232"/>
+      <c r="L35" s="233"/>
       <c r="M35" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N35" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="130">
         <v>46174</v>
@@ -6932,7 +6932,7 @@
         <v>247</v>
       </c>
       <c r="R35" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="130">
         <v>46181</v>
@@ -6944,7 +6944,7 @@
         <v>45</v>
       </c>
       <c r="V35" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="130">
         <v>46195</v>
@@ -6998,15 +6998,15 @@
       <c r="H36" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I36" s="194"/>
-      <c r="J36" s="195"/>
-      <c r="K36" s="195"/>
-      <c r="L36" s="196"/>
+      <c r="I36" s="231"/>
+      <c r="J36" s="232"/>
+      <c r="K36" s="232"/>
+      <c r="L36" s="233"/>
       <c r="M36" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N36" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="130">
         <v>46174</v>
@@ -7018,7 +7018,7 @@
         <v>247</v>
       </c>
       <c r="R36" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" s="130">
         <v>46181</v>
@@ -7030,7 +7030,7 @@
         <v>45</v>
       </c>
       <c r="V36" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="130">
         <v>46195</v>
@@ -7084,17 +7084,17 @@
       <c r="H37" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I37" s="194" t="s">
+      <c r="I37" s="231" t="s">
         <v>90</v>
       </c>
-      <c r="J37" s="195"/>
-      <c r="K37" s="195"/>
-      <c r="L37" s="196"/>
+      <c r="J37" s="232"/>
+      <c r="K37" s="232"/>
+      <c r="L37" s="233"/>
       <c r="M37" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N37" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" s="130">
         <v>46174</v>
@@ -7106,7 +7106,7 @@
         <v>247</v>
       </c>
       <c r="R37" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" s="130">
         <v>46181</v>
@@ -7118,7 +7118,7 @@
         <v>45</v>
       </c>
       <c r="V37" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="130">
         <v>46195</v>
@@ -7170,17 +7170,17 @@
       <c r="H38" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I38" s="194" t="s">
+      <c r="I38" s="231" t="s">
         <v>235</v>
       </c>
-      <c r="J38" s="195"/>
-      <c r="K38" s="195"/>
-      <c r="L38" s="196"/>
+      <c r="J38" s="232"/>
+      <c r="K38" s="232"/>
+      <c r="L38" s="233"/>
       <c r="M38" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N38" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" s="130">
         <v>46174</v>
@@ -7192,7 +7192,7 @@
         <v>247</v>
       </c>
       <c r="R38" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" s="130">
         <v>46181</v>
@@ -7204,7 +7204,7 @@
         <v>45</v>
       </c>
       <c r="V38" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="130">
         <v>46195</v>
@@ -7258,17 +7258,17 @@
       <c r="H39" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I39" s="194" t="s">
+      <c r="I39" s="231" t="s">
         <v>93</v>
       </c>
-      <c r="J39" s="195"/>
-      <c r="K39" s="195"/>
-      <c r="L39" s="196"/>
+      <c r="J39" s="232"/>
+      <c r="K39" s="232"/>
+      <c r="L39" s="233"/>
       <c r="M39" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N39" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" s="130">
         <v>46174</v>
@@ -7280,7 +7280,7 @@
         <v>247</v>
       </c>
       <c r="R39" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="130">
         <v>46181</v>
@@ -7292,7 +7292,7 @@
         <v>45</v>
       </c>
       <c r="V39" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="130">
         <v>46195</v>
@@ -7346,15 +7346,15 @@
       <c r="H40" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I40" s="194"/>
-      <c r="J40" s="195"/>
-      <c r="K40" s="195"/>
-      <c r="L40" s="196"/>
+      <c r="I40" s="231"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="233"/>
       <c r="M40" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N40" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" s="130">
         <v>46174</v>
@@ -7366,7 +7366,7 @@
         <v>247</v>
       </c>
       <c r="R40" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" s="130">
         <v>46181</v>
@@ -7378,7 +7378,7 @@
         <v>45</v>
       </c>
       <c r="V40" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="130">
         <v>46195</v>
@@ -7432,17 +7432,17 @@
       <c r="H41" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I41" s="194" t="s">
+      <c r="I41" s="231" t="s">
         <v>96</v>
       </c>
-      <c r="J41" s="195"/>
-      <c r="K41" s="195"/>
-      <c r="L41" s="196"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="233"/>
       <c r="M41" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N41" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" s="130">
         <v>46174</v>
@@ -7454,7 +7454,7 @@
         <v>247</v>
       </c>
       <c r="R41" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="130">
         <v>46181</v>
@@ -7466,7 +7466,7 @@
         <v>45</v>
       </c>
       <c r="V41" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="130">
         <v>46195</v>
@@ -7518,17 +7518,17 @@
       <c r="H42" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I42" s="194" t="s">
+      <c r="I42" s="231" t="s">
         <v>236</v>
       </c>
-      <c r="J42" s="195"/>
-      <c r="K42" s="195"/>
-      <c r="L42" s="196"/>
+      <c r="J42" s="232"/>
+      <c r="K42" s="232"/>
+      <c r="L42" s="233"/>
       <c r="M42" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N42" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" s="130">
         <v>46174</v>
@@ -7540,7 +7540,7 @@
         <v>247</v>
       </c>
       <c r="R42" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" s="130">
         <v>46181</v>
@@ -7552,7 +7552,7 @@
         <v>45</v>
       </c>
       <c r="V42" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="130">
         <v>46195</v>
@@ -7606,15 +7606,15 @@
       <c r="H43" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I43" s="194"/>
-      <c r="J43" s="195"/>
-      <c r="K43" s="195"/>
-      <c r="L43" s="196"/>
+      <c r="I43" s="231"/>
+      <c r="J43" s="232"/>
+      <c r="K43" s="232"/>
+      <c r="L43" s="233"/>
       <c r="M43" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N43" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" s="130">
         <v>46174</v>
@@ -7626,7 +7626,7 @@
         <v>247</v>
       </c>
       <c r="R43" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" s="130">
         <v>46181</v>
@@ -7638,7 +7638,7 @@
         <v>45</v>
       </c>
       <c r="V43" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="130">
         <v>46195</v>
@@ -7692,17 +7692,17 @@
       <c r="H44" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I44" s="194" t="s">
+      <c r="I44" s="231" t="s">
         <v>100</v>
       </c>
-      <c r="J44" s="195"/>
-      <c r="K44" s="195"/>
-      <c r="L44" s="196"/>
+      <c r="J44" s="232"/>
+      <c r="K44" s="232"/>
+      <c r="L44" s="233"/>
       <c r="M44" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N44" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="130">
         <v>46174</v>
@@ -7714,7 +7714,7 @@
         <v>247</v>
       </c>
       <c r="R44" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" s="130">
         <v>46181</v>
@@ -7726,7 +7726,7 @@
         <v>45</v>
       </c>
       <c r="V44" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" s="130">
         <v>46195</v>
@@ -7780,15 +7780,15 @@
       <c r="H45" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I45" s="194"/>
-      <c r="J45" s="195"/>
-      <c r="K45" s="195"/>
-      <c r="L45" s="196"/>
+      <c r="I45" s="231"/>
+      <c r="J45" s="232"/>
+      <c r="K45" s="232"/>
+      <c r="L45" s="233"/>
       <c r="M45" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N45" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" s="130">
         <v>46174</v>
@@ -7800,7 +7800,7 @@
         <v>247</v>
       </c>
       <c r="R45" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" s="130">
         <v>46181</v>
@@ -7812,7 +7812,7 @@
         <v>45</v>
       </c>
       <c r="V45" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="130">
         <v>46195</v>
@@ -7866,17 +7866,17 @@
       <c r="H46" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I46" s="194" t="s">
+      <c r="I46" s="231" t="s">
         <v>104</v>
       </c>
-      <c r="J46" s="195"/>
-      <c r="K46" s="195"/>
-      <c r="L46" s="196"/>
+      <c r="J46" s="232"/>
+      <c r="K46" s="232"/>
+      <c r="L46" s="233"/>
       <c r="M46" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N46" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" s="130">
         <v>46176</v>
@@ -7888,7 +7888,7 @@
         <v>247</v>
       </c>
       <c r="R46" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" s="130">
         <v>46181</v>
@@ -7900,7 +7900,7 @@
         <v>45</v>
       </c>
       <c r="V46" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="130">
         <v>46195</v>
@@ -7954,15 +7954,15 @@
       <c r="H47" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I47" s="194"/>
-      <c r="J47" s="195"/>
-      <c r="K47" s="195"/>
-      <c r="L47" s="196"/>
+      <c r="I47" s="231"/>
+      <c r="J47" s="232"/>
+      <c r="K47" s="232"/>
+      <c r="L47" s="233"/>
       <c r="M47" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N47" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="130">
         <v>46176</v>
@@ -7974,7 +7974,7 @@
         <v>247</v>
       </c>
       <c r="R47" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" s="130">
         <v>46181</v>
@@ -7986,7 +7986,7 @@
         <v>45</v>
       </c>
       <c r="V47" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="130">
         <v>46195</v>
@@ -8040,15 +8040,15 @@
       <c r="H48" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I48" s="194"/>
-      <c r="J48" s="195"/>
-      <c r="K48" s="195"/>
-      <c r="L48" s="196"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="232"/>
+      <c r="K48" s="232"/>
+      <c r="L48" s="233"/>
       <c r="M48" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N48" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" s="130">
         <v>46176</v>
@@ -8060,7 +8060,7 @@
         <v>247</v>
       </c>
       <c r="R48" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" s="130">
         <v>46181</v>
@@ -8072,7 +8072,7 @@
         <v>45</v>
       </c>
       <c r="V48" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="130">
         <v>46195</v>
@@ -8124,17 +8124,17 @@
       <c r="H49" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I49" s="194" t="s">
+      <c r="I49" s="231" t="s">
         <v>237</v>
       </c>
-      <c r="J49" s="195"/>
-      <c r="K49" s="195"/>
-      <c r="L49" s="196"/>
+      <c r="J49" s="232"/>
+      <c r="K49" s="232"/>
+      <c r="L49" s="233"/>
       <c r="M49" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N49" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" s="130">
         <v>46176</v>
@@ -8146,7 +8146,7 @@
         <v>247</v>
       </c>
       <c r="R49" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" s="130">
         <v>46181</v>
@@ -8158,7 +8158,7 @@
         <v>45</v>
       </c>
       <c r="V49" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W49" s="130">
         <v>46195</v>
@@ -8212,15 +8212,15 @@
       <c r="H50" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I50" s="194"/>
-      <c r="J50" s="195"/>
-      <c r="K50" s="195"/>
-      <c r="L50" s="196"/>
+      <c r="I50" s="231"/>
+      <c r="J50" s="232"/>
+      <c r="K50" s="232"/>
+      <c r="L50" s="233"/>
       <c r="M50" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N50" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" s="130">
         <v>46176</v>
@@ -8232,7 +8232,7 @@
         <v>247</v>
       </c>
       <c r="R50" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="130">
         <v>46181</v>
@@ -8244,7 +8244,7 @@
         <v>45</v>
       </c>
       <c r="V50" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="130">
         <v>46195</v>
@@ -8298,17 +8298,17 @@
       <c r="H51" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I51" s="194" t="s">
+      <c r="I51" s="231" t="s">
         <v>109</v>
       </c>
-      <c r="J51" s="195"/>
-      <c r="K51" s="195"/>
-      <c r="L51" s="196"/>
+      <c r="J51" s="232"/>
+      <c r="K51" s="232"/>
+      <c r="L51" s="233"/>
       <c r="M51" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N51" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="130">
         <v>46176</v>
@@ -8320,7 +8320,7 @@
         <v>247</v>
       </c>
       <c r="R51" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" s="130">
         <v>46181</v>
@@ -8332,7 +8332,7 @@
         <v>45</v>
       </c>
       <c r="V51" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="130">
         <v>46195</v>
@@ -8386,17 +8386,17 @@
       <c r="H52" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I52" s="194" t="s">
+      <c r="I52" s="231" t="s">
         <v>110</v>
       </c>
-      <c r="J52" s="195"/>
-      <c r="K52" s="195"/>
-      <c r="L52" s="196"/>
+      <c r="J52" s="232"/>
+      <c r="K52" s="232"/>
+      <c r="L52" s="233"/>
       <c r="M52" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N52" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" s="130">
         <v>46176</v>
@@ -8408,7 +8408,7 @@
         <v>247</v>
       </c>
       <c r="R52" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" s="130">
         <v>46181</v>
@@ -8420,7 +8420,7 @@
         <v>45</v>
       </c>
       <c r="V52" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" s="130">
         <v>46195</v>
@@ -8474,15 +8474,15 @@
       <c r="H53" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I53" s="194"/>
-      <c r="J53" s="195"/>
-      <c r="K53" s="195"/>
-      <c r="L53" s="196"/>
+      <c r="I53" s="231"/>
+      <c r="J53" s="232"/>
+      <c r="K53" s="232"/>
+      <c r="L53" s="233"/>
       <c r="M53" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N53" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" s="130">
         <v>46176</v>
@@ -8494,7 +8494,7 @@
         <v>247</v>
       </c>
       <c r="R53" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" s="130">
         <v>46181</v>
@@ -8506,7 +8506,7 @@
         <v>45</v>
       </c>
       <c r="V53" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" s="130">
         <v>46195</v>
@@ -8558,17 +8558,17 @@
       <c r="H54" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I54" s="194" t="s">
+      <c r="I54" s="231" t="s">
         <v>238</v>
       </c>
-      <c r="J54" s="195"/>
-      <c r="K54" s="195"/>
-      <c r="L54" s="196"/>
+      <c r="J54" s="232"/>
+      <c r="K54" s="232"/>
+      <c r="L54" s="233"/>
       <c r="M54" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N54" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="130">
         <v>46176</v>
@@ -8580,7 +8580,7 @@
         <v>247</v>
       </c>
       <c r="R54" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" s="130">
         <v>46181</v>
@@ -8592,7 +8592,7 @@
         <v>45</v>
       </c>
       <c r="V54" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="130">
         <v>46195</v>
@@ -8646,15 +8646,15 @@
       <c r="H55" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I55" s="194"/>
-      <c r="J55" s="195"/>
-      <c r="K55" s="195"/>
-      <c r="L55" s="196"/>
+      <c r="I55" s="231"/>
+      <c r="J55" s="232"/>
+      <c r="K55" s="232"/>
+      <c r="L55" s="233"/>
       <c r="M55" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N55" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" s="130">
         <v>46176</v>
@@ -8666,7 +8666,7 @@
         <v>247</v>
       </c>
       <c r="R55" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" s="130">
         <v>46181</v>
@@ -8678,7 +8678,7 @@
         <v>45</v>
       </c>
       <c r="V55" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="130">
         <v>46195</v>
@@ -8732,17 +8732,17 @@
       <c r="H56" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I56" s="194" t="s">
+      <c r="I56" s="231" t="s">
         <v>114</v>
       </c>
-      <c r="J56" s="195"/>
-      <c r="K56" s="195"/>
-      <c r="L56" s="196"/>
+      <c r="J56" s="232"/>
+      <c r="K56" s="232"/>
+      <c r="L56" s="233"/>
       <c r="M56" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N56" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" s="130">
         <v>46176</v>
@@ -8754,7 +8754,7 @@
         <v>247</v>
       </c>
       <c r="R56" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" s="130">
         <v>46181</v>
@@ -8766,7 +8766,7 @@
         <v>45</v>
       </c>
       <c r="V56" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="130">
         <v>46195</v>
@@ -8820,17 +8820,17 @@
       <c r="H57" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I57" s="194" t="s">
+      <c r="I57" s="231" t="s">
         <v>116</v>
       </c>
-      <c r="J57" s="195"/>
-      <c r="K57" s="195"/>
-      <c r="L57" s="196"/>
+      <c r="J57" s="232"/>
+      <c r="K57" s="232"/>
+      <c r="L57" s="233"/>
       <c r="M57" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N57" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" s="130">
         <v>46176</v>
@@ -8842,7 +8842,7 @@
         <v>247</v>
       </c>
       <c r="R57" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" s="130">
         <v>46181</v>
@@ -8854,7 +8854,7 @@
         <v>45</v>
       </c>
       <c r="V57" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" s="130">
         <v>46195</v>
@@ -8908,15 +8908,15 @@
       <c r="H58" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I58" s="194"/>
-      <c r="J58" s="195"/>
-      <c r="K58" s="195"/>
-      <c r="L58" s="196"/>
+      <c r="I58" s="231"/>
+      <c r="J58" s="232"/>
+      <c r="K58" s="232"/>
+      <c r="L58" s="233"/>
       <c r="M58" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N58" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" s="130">
         <v>46176</v>
@@ -8928,7 +8928,7 @@
         <v>247</v>
       </c>
       <c r="R58" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" s="130">
         <v>46181</v>
@@ -8940,7 +8940,7 @@
         <v>45</v>
       </c>
       <c r="V58" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="130">
         <v>46195</v>
@@ -8992,17 +8992,17 @@
       <c r="H59" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I59" s="194" t="s">
+      <c r="I59" s="231" t="s">
         <v>118</v>
       </c>
-      <c r="J59" s="195"/>
-      <c r="K59" s="195"/>
-      <c r="L59" s="196"/>
+      <c r="J59" s="232"/>
+      <c r="K59" s="232"/>
+      <c r="L59" s="233"/>
       <c r="M59" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N59" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" s="130">
         <v>46176</v>
@@ -9014,7 +9014,7 @@
         <v>247</v>
       </c>
       <c r="R59" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" s="130">
         <v>46181</v>
@@ -9026,7 +9026,7 @@
         <v>45</v>
       </c>
       <c r="V59" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="130">
         <v>46195</v>
@@ -9080,17 +9080,17 @@
       <c r="H60" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I60" s="194" t="s">
+      <c r="I60" s="231" t="s">
         <v>121</v>
       </c>
-      <c r="J60" s="195"/>
-      <c r="K60" s="195"/>
-      <c r="L60" s="196"/>
+      <c r="J60" s="232"/>
+      <c r="K60" s="232"/>
+      <c r="L60" s="233"/>
       <c r="M60" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N60" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" s="130">
         <v>46167</v>
@@ -9102,7 +9102,7 @@
         <v>247</v>
       </c>
       <c r="R60" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" s="130">
         <v>46181</v>
@@ -9114,7 +9114,7 @@
         <v>45</v>
       </c>
       <c r="V60" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W60" s="130">
         <v>46195</v>
@@ -9168,15 +9168,15 @@
       <c r="H61" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I61" s="194"/>
-      <c r="J61" s="195"/>
-      <c r="K61" s="195"/>
-      <c r="L61" s="196"/>
+      <c r="I61" s="231"/>
+      <c r="J61" s="232"/>
+      <c r="K61" s="232"/>
+      <c r="L61" s="233"/>
       <c r="M61" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N61" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" s="130">
         <v>46167</v>
@@ -9188,7 +9188,7 @@
         <v>247</v>
       </c>
       <c r="R61" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" s="130">
         <v>46181</v>
@@ -9200,7 +9200,7 @@
         <v>45</v>
       </c>
       <c r="V61" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="130">
         <v>46195</v>
@@ -9254,17 +9254,17 @@
       <c r="H62" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I62" s="194" t="s">
+      <c r="I62" s="231" t="s">
         <v>123</v>
       </c>
-      <c r="J62" s="195"/>
-      <c r="K62" s="195"/>
-      <c r="L62" s="196"/>
+      <c r="J62" s="232"/>
+      <c r="K62" s="232"/>
+      <c r="L62" s="233"/>
       <c r="M62" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N62" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" s="130">
         <v>46167</v>
@@ -9276,7 +9276,7 @@
         <v>247</v>
       </c>
       <c r="R62" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" s="130">
         <v>46181</v>
@@ -9288,7 +9288,7 @@
         <v>45</v>
       </c>
       <c r="V62" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" s="130">
         <v>46195</v>
@@ -9340,15 +9340,15 @@
       <c r="H63" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I63" s="194"/>
-      <c r="J63" s="195"/>
-      <c r="K63" s="195"/>
-      <c r="L63" s="196"/>
+      <c r="I63" s="231"/>
+      <c r="J63" s="232"/>
+      <c r="K63" s="232"/>
+      <c r="L63" s="233"/>
       <c r="M63" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N63" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" s="130">
         <v>46167</v>
@@ -9360,7 +9360,7 @@
         <v>247</v>
       </c>
       <c r="R63" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" s="130">
         <v>46181</v>
@@ -9372,7 +9372,7 @@
         <v>45</v>
       </c>
       <c r="V63" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" s="130">
         <v>46195</v>
@@ -9426,17 +9426,17 @@
       <c r="H64" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I64" s="194" t="s">
+      <c r="I64" s="231" t="s">
         <v>126</v>
       </c>
-      <c r="J64" s="195"/>
-      <c r="K64" s="195"/>
-      <c r="L64" s="196"/>
+      <c r="J64" s="232"/>
+      <c r="K64" s="232"/>
+      <c r="L64" s="233"/>
       <c r="M64" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N64" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" s="130">
         <v>46167</v>
@@ -9448,7 +9448,7 @@
         <v>247</v>
       </c>
       <c r="R64" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" s="130">
         <v>46181</v>
@@ -9460,7 +9460,7 @@
         <v>45</v>
       </c>
       <c r="V64" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" s="130">
         <v>46195</v>
@@ -9514,15 +9514,15 @@
       <c r="H65" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I65" s="194"/>
-      <c r="J65" s="195"/>
-      <c r="K65" s="195"/>
-      <c r="L65" s="196"/>
+      <c r="I65" s="231"/>
+      <c r="J65" s="232"/>
+      <c r="K65" s="232"/>
+      <c r="L65" s="233"/>
       <c r="M65" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N65" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" s="130">
         <v>46167</v>
@@ -9534,7 +9534,7 @@
         <v>247</v>
       </c>
       <c r="R65" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65" s="130">
         <v>46181</v>
@@ -9546,7 +9546,7 @@
         <v>45</v>
       </c>
       <c r="V65" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" s="130">
         <v>46195</v>
@@ -9600,17 +9600,17 @@
       <c r="H66" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I66" s="194" t="s">
+      <c r="I66" s="231" t="s">
         <v>129</v>
       </c>
-      <c r="J66" s="195"/>
-      <c r="K66" s="195"/>
-      <c r="L66" s="196"/>
+      <c r="J66" s="232"/>
+      <c r="K66" s="232"/>
+      <c r="L66" s="233"/>
       <c r="M66" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N66" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" s="130">
         <v>46167</v>
@@ -9622,7 +9622,7 @@
         <v>247</v>
       </c>
       <c r="R66" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" s="130">
         <v>46181</v>
@@ -9634,7 +9634,7 @@
         <v>45</v>
       </c>
       <c r="V66" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="130">
         <v>46195</v>
@@ -9688,17 +9688,17 @@
       <c r="H67" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I67" s="194" t="s">
+      <c r="I67" s="231" t="s">
         <v>131</v>
       </c>
-      <c r="J67" s="195"/>
-      <c r="K67" s="195"/>
-      <c r="L67" s="196"/>
+      <c r="J67" s="232"/>
+      <c r="K67" s="232"/>
+      <c r="L67" s="233"/>
       <c r="M67" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N67" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" s="130">
         <v>46167</v>
@@ -9710,7 +9710,7 @@
         <v>247</v>
       </c>
       <c r="R67" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S67" s="130">
         <v>46181</v>
@@ -9722,7 +9722,7 @@
         <v>45</v>
       </c>
       <c r="V67" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" s="130">
         <v>46195</v>
@@ -9774,17 +9774,17 @@
       <c r="H68" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I68" s="194" t="s">
+      <c r="I68" s="231" t="s">
         <v>133</v>
       </c>
-      <c r="J68" s="195"/>
-      <c r="K68" s="195"/>
-      <c r="L68" s="196"/>
+      <c r="J68" s="232"/>
+      <c r="K68" s="232"/>
+      <c r="L68" s="233"/>
       <c r="M68" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N68" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" s="130">
         <v>46167</v>
@@ -9796,7 +9796,7 @@
         <v>247</v>
       </c>
       <c r="R68" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S68" s="130">
         <v>46181</v>
@@ -9808,7 +9808,7 @@
         <v>45</v>
       </c>
       <c r="V68" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="130">
         <v>46195</v>
@@ -9862,17 +9862,17 @@
       <c r="H69" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I69" s="194" t="s">
+      <c r="I69" s="231" t="s">
         <v>137</v>
       </c>
-      <c r="J69" s="195"/>
-      <c r="K69" s="195"/>
-      <c r="L69" s="196"/>
+      <c r="J69" s="232"/>
+      <c r="K69" s="232"/>
+      <c r="L69" s="233"/>
       <c r="M69" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N69" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" s="130">
         <v>46174</v>
@@ -9884,7 +9884,7 @@
         <v>247</v>
       </c>
       <c r="R69" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69" s="130">
         <v>46181</v>
@@ -9896,7 +9896,7 @@
         <v>45</v>
       </c>
       <c r="V69" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" s="130">
         <v>46195</v>
@@ -9948,17 +9948,17 @@
       <c r="H70" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I70" s="194" t="s">
+      <c r="I70" s="231" t="s">
         <v>139</v>
       </c>
-      <c r="J70" s="195"/>
-      <c r="K70" s="195"/>
-      <c r="L70" s="196"/>
+      <c r="J70" s="232"/>
+      <c r="K70" s="232"/>
+      <c r="L70" s="233"/>
       <c r="M70" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N70" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" s="130">
         <v>46174</v>
@@ -9970,7 +9970,7 @@
         <v>247</v>
       </c>
       <c r="R70" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" s="130">
         <v>46181</v>
@@ -9982,7 +9982,7 @@
         <v>45</v>
       </c>
       <c r="V70" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W70" s="130">
         <v>46195</v>
@@ -10038,17 +10038,17 @@
       <c r="H71" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I71" s="194" t="s">
+      <c r="I71" s="231" t="s">
         <v>143</v>
       </c>
-      <c r="J71" s="195"/>
-      <c r="K71" s="195"/>
-      <c r="L71" s="196"/>
+      <c r="J71" s="232"/>
+      <c r="K71" s="232"/>
+      <c r="L71" s="233"/>
       <c r="M71" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N71" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" s="130">
         <v>46162</v>
@@ -10060,7 +10060,7 @@
         <v>247</v>
       </c>
       <c r="R71" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71" s="130">
         <v>46174</v>
@@ -10072,7 +10072,7 @@
         <v>45</v>
       </c>
       <c r="V71" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" s="130">
         <v>46195</v>
@@ -10124,17 +10124,17 @@
       <c r="H72" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I72" s="194" t="s">
+      <c r="I72" s="231" t="s">
         <v>145</v>
       </c>
-      <c r="J72" s="195"/>
-      <c r="K72" s="195"/>
-      <c r="L72" s="196"/>
+      <c r="J72" s="232"/>
+      <c r="K72" s="232"/>
+      <c r="L72" s="233"/>
       <c r="M72" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N72" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" s="130">
         <v>46162</v>
@@ -10146,7 +10146,7 @@
         <v>247</v>
       </c>
       <c r="R72" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" s="130">
         <v>46174</v>
@@ -10158,7 +10158,7 @@
         <v>45</v>
       </c>
       <c r="V72" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="130">
         <v>46195</v>
@@ -10212,17 +10212,17 @@
       <c r="H73" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I73" s="194" t="s">
+      <c r="I73" s="231" t="s">
         <v>148</v>
       </c>
-      <c r="J73" s="195"/>
-      <c r="K73" s="195"/>
-      <c r="L73" s="196"/>
+      <c r="J73" s="232"/>
+      <c r="K73" s="232"/>
+      <c r="L73" s="233"/>
       <c r="M73" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N73" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" s="130">
         <v>46162</v>
@@ -10234,7 +10234,7 @@
         <v>247</v>
       </c>
       <c r="R73" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" s="130">
         <v>46174</v>
@@ -10246,7 +10246,7 @@
         <v>45</v>
       </c>
       <c r="V73" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="130">
         <v>46195</v>
@@ -10300,17 +10300,17 @@
       <c r="H74" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I74" s="194" t="s">
+      <c r="I74" s="231" t="s">
         <v>150</v>
       </c>
-      <c r="J74" s="195"/>
-      <c r="K74" s="195"/>
-      <c r="L74" s="196"/>
+      <c r="J74" s="232"/>
+      <c r="K74" s="232"/>
+      <c r="L74" s="233"/>
       <c r="M74" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N74" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" s="130">
         <v>46162</v>
@@ -10322,7 +10322,7 @@
         <v>247</v>
       </c>
       <c r="R74" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74" s="130">
         <v>46174</v>
@@ -10334,7 +10334,7 @@
         <v>45</v>
       </c>
       <c r="V74" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="130">
         <v>46195</v>
@@ -10386,15 +10386,15 @@
       <c r="H75" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I75" s="194"/>
-      <c r="J75" s="195"/>
-      <c r="K75" s="195"/>
-      <c r="L75" s="196"/>
+      <c r="I75" s="231"/>
+      <c r="J75" s="232"/>
+      <c r="K75" s="232"/>
+      <c r="L75" s="233"/>
       <c r="M75" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N75" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" s="130">
         <v>46162</v>
@@ -10406,7 +10406,7 @@
         <v>247</v>
       </c>
       <c r="R75" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" s="130">
         <v>46174</v>
@@ -10418,7 +10418,7 @@
         <v>45</v>
       </c>
       <c r="V75" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W75" s="130">
         <v>46195</v>
@@ -10472,15 +10472,15 @@
       <c r="H76" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I76" s="194"/>
-      <c r="J76" s="195"/>
-      <c r="K76" s="195"/>
-      <c r="L76" s="196"/>
+      <c r="I76" s="231"/>
+      <c r="J76" s="232"/>
+      <c r="K76" s="232"/>
+      <c r="L76" s="233"/>
       <c r="M76" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N76" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" s="130">
         <v>46176</v>
@@ -10492,7 +10492,7 @@
         <v>247</v>
       </c>
       <c r="R76" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76" s="130">
         <v>46188</v>
@@ -10504,7 +10504,7 @@
         <v>45</v>
       </c>
       <c r="V76" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="130">
         <v>46196</v>
@@ -10556,15 +10556,15 @@
       <c r="H77" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I77" s="194"/>
-      <c r="J77" s="195"/>
-      <c r="K77" s="195"/>
-      <c r="L77" s="196"/>
+      <c r="I77" s="231"/>
+      <c r="J77" s="232"/>
+      <c r="K77" s="232"/>
+      <c r="L77" s="233"/>
       <c r="M77" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N77" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" s="130">
         <v>46176</v>
@@ -10576,7 +10576,7 @@
         <v>247</v>
       </c>
       <c r="R77" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" s="130">
         <v>46188</v>
@@ -10588,7 +10588,7 @@
         <v>45</v>
       </c>
       <c r="V77" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" s="130">
         <v>46196</v>
@@ -10640,15 +10640,15 @@
       <c r="H78" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I78" s="194"/>
-      <c r="J78" s="195"/>
-      <c r="K78" s="195"/>
-      <c r="L78" s="196"/>
+      <c r="I78" s="231"/>
+      <c r="J78" s="232"/>
+      <c r="K78" s="232"/>
+      <c r="L78" s="233"/>
       <c r="M78" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N78" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" s="130">
         <v>46176</v>
@@ -10660,7 +10660,7 @@
         <v>247</v>
       </c>
       <c r="R78" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S78" s="130">
         <v>46188</v>
@@ -10672,7 +10672,7 @@
         <v>45</v>
       </c>
       <c r="V78" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" s="130">
         <v>46196</v>
@@ -10726,17 +10726,17 @@
       <c r="H79" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I79" s="194" t="s">
+      <c r="I79" s="231" t="s">
         <v>157</v>
       </c>
-      <c r="J79" s="195"/>
-      <c r="K79" s="195"/>
-      <c r="L79" s="196"/>
+      <c r="J79" s="232"/>
+      <c r="K79" s="232"/>
+      <c r="L79" s="233"/>
       <c r="M79" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N79" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" s="130">
         <v>46174</v>
@@ -10748,7 +10748,7 @@
         <v>247</v>
       </c>
       <c r="R79" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S79" s="130">
         <v>46181</v>
@@ -10760,7 +10760,7 @@
         <v>45</v>
       </c>
       <c r="V79" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W79" s="130">
         <v>46195</v>
@@ -10814,15 +10814,15 @@
       <c r="H80" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I80" s="194"/>
-      <c r="J80" s="195"/>
-      <c r="K80" s="195"/>
-      <c r="L80" s="196"/>
+      <c r="I80" s="231"/>
+      <c r="J80" s="232"/>
+      <c r="K80" s="232"/>
+      <c r="L80" s="233"/>
       <c r="M80" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N80" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" s="130">
         <v>46174</v>
@@ -10834,7 +10834,7 @@
         <v>247</v>
       </c>
       <c r="R80" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S80" s="130">
         <v>46181</v>
@@ -10846,7 +10846,7 @@
         <v>45</v>
       </c>
       <c r="V80" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="130">
         <v>46195</v>
@@ -10900,17 +10900,17 @@
       <c r="H81" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I81" s="194" t="s">
+      <c r="I81" s="231" t="s">
         <v>239</v>
       </c>
-      <c r="J81" s="195"/>
-      <c r="K81" s="195"/>
-      <c r="L81" s="196"/>
+      <c r="J81" s="232"/>
+      <c r="K81" s="232"/>
+      <c r="L81" s="233"/>
       <c r="M81" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N81" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" s="130">
         <v>46174</v>
@@ -10922,7 +10922,7 @@
         <v>247</v>
       </c>
       <c r="R81" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S81" s="130">
         <v>46181</v>
@@ -10934,7 +10934,7 @@
         <v>45</v>
       </c>
       <c r="V81" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W81" s="130">
         <v>46195</v>
@@ -10988,17 +10988,17 @@
       <c r="H82" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I82" s="194" t="s">
+      <c r="I82" s="231" t="s">
         <v>240</v>
       </c>
-      <c r="J82" s="195"/>
-      <c r="K82" s="195"/>
-      <c r="L82" s="196"/>
+      <c r="J82" s="232"/>
+      <c r="K82" s="232"/>
+      <c r="L82" s="233"/>
       <c r="M82" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N82" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" s="130">
         <v>46174</v>
@@ -11010,7 +11010,7 @@
         <v>247</v>
       </c>
       <c r="R82" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S82" s="130">
         <v>46181</v>
@@ -11022,7 +11022,7 @@
         <v>45</v>
       </c>
       <c r="V82" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" s="130">
         <v>46195</v>
@@ -11076,15 +11076,15 @@
       <c r="H83" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I83" s="194"/>
-      <c r="J83" s="195"/>
-      <c r="K83" s="195"/>
-      <c r="L83" s="196"/>
+      <c r="I83" s="231"/>
+      <c r="J83" s="232"/>
+      <c r="K83" s="232"/>
+      <c r="L83" s="233"/>
       <c r="M83" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N83" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" s="130">
         <v>46174</v>
@@ -11096,7 +11096,7 @@
         <v>247</v>
       </c>
       <c r="R83" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S83" s="130">
         <v>46181</v>
@@ -11108,7 +11108,7 @@
         <v>45</v>
       </c>
       <c r="V83" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W83" s="130">
         <v>46195</v>
@@ -11162,17 +11162,17 @@
       <c r="H84" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I84" s="194" t="s">
+      <c r="I84" s="231" t="s">
         <v>163</v>
       </c>
-      <c r="J84" s="195"/>
-      <c r="K84" s="195"/>
-      <c r="L84" s="196"/>
+      <c r="J84" s="232"/>
+      <c r="K84" s="232"/>
+      <c r="L84" s="233"/>
       <c r="M84" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N84" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" s="130">
         <v>46174</v>
@@ -11184,7 +11184,7 @@
         <v>247</v>
       </c>
       <c r="R84" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S84" s="130">
         <v>46181</v>
@@ -11196,7 +11196,7 @@
         <v>45</v>
       </c>
       <c r="V84" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W84" s="130">
         <v>46195</v>
@@ -11250,15 +11250,15 @@
       <c r="H85" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I85" s="194"/>
-      <c r="J85" s="195"/>
-      <c r="K85" s="195"/>
-      <c r="L85" s="196"/>
+      <c r="I85" s="231"/>
+      <c r="J85" s="232"/>
+      <c r="K85" s="232"/>
+      <c r="L85" s="233"/>
       <c r="M85" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N85" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" s="130">
         <v>46174</v>
@@ -11270,7 +11270,7 @@
         <v>247</v>
       </c>
       <c r="R85" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" s="130">
         <v>46181</v>
@@ -11282,7 +11282,7 @@
         <v>45</v>
       </c>
       <c r="V85" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="130">
         <v>46195</v>
@@ -11336,17 +11336,17 @@
       <c r="H86" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I86" s="194" t="s">
+      <c r="I86" s="231" t="s">
         <v>241</v>
       </c>
-      <c r="J86" s="195"/>
-      <c r="K86" s="195"/>
-      <c r="L86" s="196"/>
+      <c r="J86" s="232"/>
+      <c r="K86" s="232"/>
+      <c r="L86" s="233"/>
       <c r="M86" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N86" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" s="130">
         <v>46174</v>
@@ -11358,7 +11358,7 @@
         <v>247</v>
       </c>
       <c r="R86" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S86" s="130">
         <v>46181</v>
@@ -11370,7 +11370,7 @@
         <v>45</v>
       </c>
       <c r="V86" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W86" s="130">
         <v>46195</v>
@@ -11424,17 +11424,17 @@
       <c r="H87" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I87" s="194" t="s">
+      <c r="I87" s="231" t="s">
         <v>243</v>
       </c>
-      <c r="J87" s="195"/>
-      <c r="K87" s="195"/>
-      <c r="L87" s="196"/>
+      <c r="J87" s="232"/>
+      <c r="K87" s="232"/>
+      <c r="L87" s="233"/>
       <c r="M87" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N87" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" s="130">
         <v>46174</v>
@@ -11446,7 +11446,7 @@
         <v>247</v>
       </c>
       <c r="R87" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" s="130">
         <v>46181</v>
@@ -11458,7 +11458,7 @@
         <v>45</v>
       </c>
       <c r="V87" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W87" s="130">
         <v>46195</v>
@@ -11512,17 +11512,17 @@
       <c r="H88" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I88" s="194" t="s">
+      <c r="I88" s="231" t="s">
         <v>242</v>
       </c>
-      <c r="J88" s="195"/>
-      <c r="K88" s="195"/>
-      <c r="L88" s="196"/>
+      <c r="J88" s="232"/>
+      <c r="K88" s="232"/>
+      <c r="L88" s="233"/>
       <c r="M88" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N88" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" s="130">
         <v>46174</v>
@@ -11534,7 +11534,7 @@
         <v>247</v>
       </c>
       <c r="R88" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S88" s="130">
         <v>46181</v>
@@ -11546,7 +11546,7 @@
         <v>45</v>
       </c>
       <c r="V88" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="130">
         <v>46195</v>
@@ -11600,15 +11600,15 @@
       <c r="H89" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I89" s="194"/>
-      <c r="J89" s="195"/>
-      <c r="K89" s="195"/>
-      <c r="L89" s="196"/>
+      <c r="I89" s="231"/>
+      <c r="J89" s="232"/>
+      <c r="K89" s="232"/>
+      <c r="L89" s="233"/>
       <c r="M89" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N89" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" s="130">
         <v>46174</v>
@@ -11620,7 +11620,7 @@
         <v>247</v>
       </c>
       <c r="R89" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S89" s="130">
         <v>46181</v>
@@ -11632,7 +11632,7 @@
         <v>45</v>
       </c>
       <c r="V89" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W89" s="130">
         <v>46195</v>
@@ -11684,15 +11684,15 @@
       <c r="H90" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I90" s="194"/>
-      <c r="J90" s="195"/>
-      <c r="K90" s="195"/>
-      <c r="L90" s="196"/>
+      <c r="I90" s="231"/>
+      <c r="J90" s="232"/>
+      <c r="K90" s="232"/>
+      <c r="L90" s="233"/>
       <c r="M90" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N90" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" s="130">
         <v>46174</v>
@@ -11704,7 +11704,7 @@
         <v>247</v>
       </c>
       <c r="R90" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S90" s="130">
         <v>46181</v>
@@ -11716,7 +11716,7 @@
         <v>45</v>
       </c>
       <c r="V90" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W90" s="130">
         <v>46195</v>
@@ -11770,17 +11770,17 @@
       <c r="H91" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I91" s="194" t="s">
+      <c r="I91" s="231" t="s">
         <v>171</v>
       </c>
-      <c r="J91" s="195"/>
-      <c r="K91" s="195"/>
-      <c r="L91" s="196"/>
+      <c r="J91" s="232"/>
+      <c r="K91" s="232"/>
+      <c r="L91" s="233"/>
       <c r="M91" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N91" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" s="130">
         <v>46174</v>
@@ -11792,7 +11792,7 @@
         <v>247</v>
       </c>
       <c r="R91" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S91" s="130">
         <v>46181</v>
@@ -11804,7 +11804,7 @@
         <v>45</v>
       </c>
       <c r="V91" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W91" s="130">
         <v>46195</v>
@@ -11858,15 +11858,15 @@
       <c r="H92" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I92" s="194"/>
-      <c r="J92" s="195"/>
-      <c r="K92" s="195"/>
-      <c r="L92" s="196"/>
+      <c r="I92" s="231"/>
+      <c r="J92" s="232"/>
+      <c r="K92" s="232"/>
+      <c r="L92" s="233"/>
       <c r="M92" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N92" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" s="130">
         <v>46174</v>
@@ -11878,7 +11878,7 @@
         <v>247</v>
       </c>
       <c r="R92" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S92" s="130">
         <v>46181</v>
@@ -11890,7 +11890,7 @@
         <v>45</v>
       </c>
       <c r="V92" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="130">
         <v>46195</v>
@@ -11944,17 +11944,17 @@
       <c r="H93" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I93" s="194" t="s">
+      <c r="I93" s="231" t="s">
         <v>163</v>
       </c>
-      <c r="J93" s="195"/>
-      <c r="K93" s="195"/>
-      <c r="L93" s="196"/>
+      <c r="J93" s="232"/>
+      <c r="K93" s="232"/>
+      <c r="L93" s="233"/>
       <c r="M93" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N93" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" s="130">
         <v>46174</v>
@@ -11966,7 +11966,7 @@
         <v>247</v>
       </c>
       <c r="R93" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S93" s="130">
         <v>46181</v>
@@ -11978,7 +11978,7 @@
         <v>45</v>
       </c>
       <c r="V93" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" s="130">
         <v>46195</v>
@@ -12032,15 +12032,15 @@
       <c r="H94" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I94" s="194"/>
-      <c r="J94" s="195"/>
-      <c r="K94" s="195"/>
-      <c r="L94" s="196"/>
+      <c r="I94" s="231"/>
+      <c r="J94" s="232"/>
+      <c r="K94" s="232"/>
+      <c r="L94" s="233"/>
       <c r="M94" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N94" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" s="130">
         <v>46176</v>
@@ -12052,7 +12052,7 @@
         <v>247</v>
       </c>
       <c r="R94" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94" s="130">
         <v>46188</v>
@@ -12064,7 +12064,7 @@
         <v>45</v>
       </c>
       <c r="V94" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W94" s="130">
         <v>46196</v>
@@ -12118,15 +12118,15 @@
       <c r="H95" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I95" s="194"/>
-      <c r="J95" s="195"/>
-      <c r="K95" s="195"/>
-      <c r="L95" s="196"/>
+      <c r="I95" s="231"/>
+      <c r="J95" s="232"/>
+      <c r="K95" s="232"/>
+      <c r="L95" s="233"/>
       <c r="M95" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N95" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" s="130">
         <v>46176</v>
@@ -12138,7 +12138,7 @@
         <v>247</v>
       </c>
       <c r="R95" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S95" s="130">
         <v>46188</v>
@@ -12150,7 +12150,7 @@
         <v>45</v>
       </c>
       <c r="V95" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W95" s="130">
         <v>46196</v>
@@ -12204,15 +12204,15 @@
       <c r="H96" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I96" s="194"/>
-      <c r="J96" s="195"/>
-      <c r="K96" s="195"/>
-      <c r="L96" s="196"/>
+      <c r="I96" s="231"/>
+      <c r="J96" s="232"/>
+      <c r="K96" s="232"/>
+      <c r="L96" s="233"/>
       <c r="M96" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N96" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" s="130">
         <v>46176</v>
@@ -12224,7 +12224,7 @@
         <v>247</v>
       </c>
       <c r="R96" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S96" s="130">
         <v>46188</v>
@@ -12236,7 +12236,7 @@
         <v>45</v>
       </c>
       <c r="V96" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W96" s="130">
         <v>46196</v>
@@ -12290,15 +12290,15 @@
       <c r="H97" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I97" s="194"/>
-      <c r="J97" s="195"/>
-      <c r="K97" s="195"/>
-      <c r="L97" s="196"/>
+      <c r="I97" s="231"/>
+      <c r="J97" s="232"/>
+      <c r="K97" s="232"/>
+      <c r="L97" s="233"/>
       <c r="M97" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N97" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" s="130">
         <v>46176</v>
@@ -12310,7 +12310,7 @@
         <v>247</v>
       </c>
       <c r="R97" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S97" s="130">
         <v>46188</v>
@@ -12322,7 +12322,7 @@
         <v>45</v>
       </c>
       <c r="V97" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" s="130">
         <v>46196</v>
@@ -12374,17 +12374,17 @@
       <c r="H98" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I98" s="194" t="s">
+      <c r="I98" s="231" t="s">
         <v>244</v>
       </c>
-      <c r="J98" s="195"/>
-      <c r="K98" s="195"/>
-      <c r="L98" s="196"/>
+      <c r="J98" s="232"/>
+      <c r="K98" s="232"/>
+      <c r="L98" s="233"/>
       <c r="M98" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N98" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" s="130">
         <v>46176</v>
@@ -12396,7 +12396,7 @@
         <v>247</v>
       </c>
       <c r="R98" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S98" s="130">
         <v>46188</v>
@@ -12408,7 +12408,7 @@
         <v>45</v>
       </c>
       <c r="V98" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W98" s="130">
         <v>46196</v>
@@ -12462,15 +12462,15 @@
       <c r="H99" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I99" s="194"/>
-      <c r="J99" s="195"/>
-      <c r="K99" s="195"/>
-      <c r="L99" s="196"/>
+      <c r="I99" s="231"/>
+      <c r="J99" s="232"/>
+      <c r="K99" s="232"/>
+      <c r="L99" s="233"/>
       <c r="M99" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N99" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" s="130">
         <v>46176</v>
@@ -12482,7 +12482,7 @@
         <v>247</v>
       </c>
       <c r="R99" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S99" s="130">
         <v>46188</v>
@@ -12494,7 +12494,7 @@
         <v>45</v>
       </c>
       <c r="V99" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W99" s="130">
         <v>46196</v>
@@ -12548,15 +12548,15 @@
       <c r="H100" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I100" s="194"/>
-      <c r="J100" s="195"/>
-      <c r="K100" s="195"/>
-      <c r="L100" s="196"/>
+      <c r="I100" s="231"/>
+      <c r="J100" s="232"/>
+      <c r="K100" s="232"/>
+      <c r="L100" s="233"/>
       <c r="M100" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N100" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" s="130">
         <v>46176</v>
@@ -12568,7 +12568,7 @@
         <v>247</v>
       </c>
       <c r="R100" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S100" s="130">
         <v>46188</v>
@@ -12580,7 +12580,7 @@
         <v>45</v>
       </c>
       <c r="V100" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W100" s="130">
         <v>46196</v>
@@ -12634,17 +12634,17 @@
       <c r="H101" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I101" s="194" t="s">
+      <c r="I101" s="231" t="s">
         <v>184</v>
       </c>
-      <c r="J101" s="195"/>
-      <c r="K101" s="195"/>
-      <c r="L101" s="196"/>
+      <c r="J101" s="232"/>
+      <c r="K101" s="232"/>
+      <c r="L101" s="233"/>
       <c r="M101" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N101" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101" s="130">
         <v>46177</v>
@@ -12656,7 +12656,7 @@
         <v>247</v>
       </c>
       <c r="R101" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S101" s="130">
         <v>46188</v>
@@ -12668,7 +12668,7 @@
         <v>45</v>
       </c>
       <c r="V101" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" s="130">
         <v>46196</v>
@@ -12722,15 +12722,15 @@
       <c r="H102" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I102" s="194"/>
-      <c r="J102" s="195"/>
-      <c r="K102" s="195"/>
-      <c r="L102" s="196"/>
+      <c r="I102" s="231"/>
+      <c r="J102" s="232"/>
+      <c r="K102" s="232"/>
+      <c r="L102" s="233"/>
       <c r="M102" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N102" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O102" s="130">
         <v>46177</v>
@@ -12742,7 +12742,7 @@
         <v>247</v>
       </c>
       <c r="R102" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S102" s="130">
         <v>46188</v>
@@ -12754,7 +12754,7 @@
         <v>45</v>
       </c>
       <c r="V102" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="130">
         <v>46196</v>
@@ -12808,15 +12808,15 @@
       <c r="H103" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I103" s="194"/>
-      <c r="J103" s="195"/>
-      <c r="K103" s="195"/>
-      <c r="L103" s="196"/>
+      <c r="I103" s="231"/>
+      <c r="J103" s="232"/>
+      <c r="K103" s="232"/>
+      <c r="L103" s="233"/>
       <c r="M103" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N103" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O103" s="130">
         <v>46177</v>
@@ -12828,7 +12828,7 @@
         <v>247</v>
       </c>
       <c r="R103" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S103" s="130">
         <v>46188</v>
@@ -12840,7 +12840,7 @@
         <v>45</v>
       </c>
       <c r="V103" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W103" s="130">
         <v>46196</v>
@@ -12894,15 +12894,15 @@
       <c r="H104" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I104" s="194"/>
-      <c r="J104" s="195"/>
-      <c r="K104" s="195"/>
-      <c r="L104" s="196"/>
+      <c r="I104" s="231"/>
+      <c r="J104" s="232"/>
+      <c r="K104" s="232"/>
+      <c r="L104" s="233"/>
       <c r="M104" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N104" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" s="130">
         <v>46177</v>
@@ -12914,7 +12914,7 @@
         <v>247</v>
       </c>
       <c r="R104" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S104" s="130">
         <v>46188</v>
@@ -12926,7 +12926,7 @@
         <v>45</v>
       </c>
       <c r="V104" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W104" s="130">
         <v>46196</v>
@@ -12980,15 +12980,15 @@
       <c r="H105" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I105" s="194"/>
-      <c r="J105" s="195"/>
-      <c r="K105" s="195"/>
-      <c r="L105" s="196"/>
+      <c r="I105" s="231"/>
+      <c r="J105" s="232"/>
+      <c r="K105" s="232"/>
+      <c r="L105" s="233"/>
       <c r="M105" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N105" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105" s="130">
         <v>46177</v>
@@ -13000,7 +13000,7 @@
         <v>247</v>
       </c>
       <c r="R105" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S105" s="130">
         <v>46188</v>
@@ -13012,7 +13012,7 @@
         <v>45</v>
       </c>
       <c r="V105" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W105" s="130">
         <v>46196</v>
@@ -13064,15 +13064,15 @@
       <c r="H106" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I106" s="194"/>
-      <c r="J106" s="195"/>
-      <c r="K106" s="195"/>
-      <c r="L106" s="196"/>
+      <c r="I106" s="231"/>
+      <c r="J106" s="232"/>
+      <c r="K106" s="232"/>
+      <c r="L106" s="233"/>
       <c r="M106" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N106" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O106" s="130">
         <v>46177</v>
@@ -13084,7 +13084,7 @@
         <v>247</v>
       </c>
       <c r="R106" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S106" s="130">
         <v>46188</v>
@@ -13096,7 +13096,7 @@
         <v>45</v>
       </c>
       <c r="V106" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" s="130">
         <v>46196</v>
@@ -13150,15 +13150,15 @@
       <c r="H107" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I107" s="194"/>
-      <c r="J107" s="195"/>
-      <c r="K107" s="195"/>
-      <c r="L107" s="196"/>
+      <c r="I107" s="231"/>
+      <c r="J107" s="232"/>
+      <c r="K107" s="232"/>
+      <c r="L107" s="233"/>
       <c r="M107" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N107" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O107" s="130">
         <v>46177</v>
@@ -13170,7 +13170,7 @@
         <v>247</v>
       </c>
       <c r="R107" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S107" s="130">
         <v>46188</v>
@@ -13182,7 +13182,7 @@
         <v>45</v>
       </c>
       <c r="V107" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W107" s="130">
         <v>46196</v>
@@ -13236,15 +13236,15 @@
       <c r="H108" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I108" s="194"/>
-      <c r="J108" s="195"/>
-      <c r="K108" s="195"/>
-      <c r="L108" s="196"/>
+      <c r="I108" s="231"/>
+      <c r="J108" s="232"/>
+      <c r="K108" s="232"/>
+      <c r="L108" s="233"/>
       <c r="M108" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N108" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O108" s="130">
         <v>46177</v>
@@ -13256,7 +13256,7 @@
         <v>247</v>
       </c>
       <c r="R108" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S108" s="130">
         <v>46188</v>
@@ -13268,7 +13268,7 @@
         <v>45</v>
       </c>
       <c r="V108" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W108" s="130">
         <v>46196</v>
@@ -13322,15 +13322,15 @@
       <c r="H109" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I109" s="194"/>
-      <c r="J109" s="195"/>
-      <c r="K109" s="195"/>
-      <c r="L109" s="196"/>
+      <c r="I109" s="231"/>
+      <c r="J109" s="232"/>
+      <c r="K109" s="232"/>
+      <c r="L109" s="233"/>
       <c r="M109" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N109" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O109" s="140">
         <v>46177</v>
@@ -13342,7 +13342,7 @@
         <v>247</v>
       </c>
       <c r="R109" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S109" s="72">
         <v>46188</v>
@@ -13354,7 +13354,7 @@
         <v>45</v>
       </c>
       <c r="V109" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" s="130">
         <v>46196</v>
@@ -13408,15 +13408,15 @@
       <c r="H110" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I110" s="194"/>
-      <c r="J110" s="195"/>
-      <c r="K110" s="195"/>
-      <c r="L110" s="196"/>
+      <c r="I110" s="231"/>
+      <c r="J110" s="232"/>
+      <c r="K110" s="232"/>
+      <c r="L110" s="233"/>
       <c r="M110" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N110" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O110" s="140">
         <v>46177</v>
@@ -13428,7 +13428,7 @@
         <v>247</v>
       </c>
       <c r="R110" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S110" s="72">
         <v>46188</v>
@@ -13440,7 +13440,7 @@
         <v>45</v>
       </c>
       <c r="V110" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W110" s="130">
         <v>46196</v>
@@ -13492,15 +13492,15 @@
       <c r="H111" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I111" s="194"/>
-      <c r="J111" s="195"/>
-      <c r="K111" s="195"/>
-      <c r="L111" s="196"/>
+      <c r="I111" s="231"/>
+      <c r="J111" s="232"/>
+      <c r="K111" s="232"/>
+      <c r="L111" s="233"/>
       <c r="M111" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N111" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" s="140">
         <v>46177</v>
@@ -13512,7 +13512,7 @@
         <v>247</v>
       </c>
       <c r="R111" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S111" s="72">
         <v>46188</v>
@@ -13524,7 +13524,7 @@
         <v>45</v>
       </c>
       <c r="V111" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W111" s="130">
         <v>46196</v>
@@ -13578,15 +13578,15 @@
       <c r="H112" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I112" s="194"/>
-      <c r="J112" s="195"/>
-      <c r="K112" s="195"/>
-      <c r="L112" s="196"/>
+      <c r="I112" s="231"/>
+      <c r="J112" s="232"/>
+      <c r="K112" s="232"/>
+      <c r="L112" s="233"/>
       <c r="M112" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N112" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" s="140">
         <v>46177</v>
@@ -13598,7 +13598,7 @@
         <v>247</v>
       </c>
       <c r="R112" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S112" s="72">
         <v>46188</v>
@@ -13610,7 +13610,7 @@
         <v>45</v>
       </c>
       <c r="V112" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W112" s="130">
         <v>46196</v>
@@ -13664,15 +13664,15 @@
       <c r="H113" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I113" s="194"/>
-      <c r="J113" s="195"/>
-      <c r="K113" s="195"/>
-      <c r="L113" s="196"/>
+      <c r="I113" s="231"/>
+      <c r="J113" s="232"/>
+      <c r="K113" s="232"/>
+      <c r="L113" s="233"/>
       <c r="M113" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N113" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113" s="140">
         <v>46177</v>
@@ -13684,7 +13684,7 @@
         <v>247</v>
       </c>
       <c r="R113" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S113" s="72">
         <v>46188</v>
@@ -13696,7 +13696,7 @@
         <v>45</v>
       </c>
       <c r="V113" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W113" s="130">
         <v>46196</v>
@@ -13750,15 +13750,15 @@
       <c r="H114" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I114" s="194"/>
-      <c r="J114" s="195"/>
-      <c r="K114" s="195"/>
-      <c r="L114" s="196"/>
+      <c r="I114" s="231"/>
+      <c r="J114" s="232"/>
+      <c r="K114" s="232"/>
+      <c r="L114" s="233"/>
       <c r="M114" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N114" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" s="140">
         <v>46177</v>
@@ -13770,7 +13770,7 @@
         <v>247</v>
       </c>
       <c r="R114" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S114" s="72">
         <v>46188</v>
@@ -13782,7 +13782,7 @@
         <v>45</v>
       </c>
       <c r="V114" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W114" s="130">
         <v>46196</v>
@@ -13834,15 +13834,15 @@
       <c r="H115" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I115" s="194"/>
-      <c r="J115" s="195"/>
-      <c r="K115" s="195"/>
-      <c r="L115" s="196"/>
+      <c r="I115" s="231"/>
+      <c r="J115" s="232"/>
+      <c r="K115" s="232"/>
+      <c r="L115" s="233"/>
       <c r="M115" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N115" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O115" s="140">
         <v>46177</v>
@@ -13854,7 +13854,7 @@
         <v>247</v>
       </c>
       <c r="R115" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S115" s="72">
         <v>46188</v>
@@ -13866,7 +13866,7 @@
         <v>45</v>
       </c>
       <c r="V115" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W115" s="130">
         <v>46196</v>
@@ -13920,15 +13920,15 @@
       <c r="H116" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I116" s="194"/>
-      <c r="J116" s="195"/>
-      <c r="K116" s="195"/>
-      <c r="L116" s="196"/>
+      <c r="I116" s="231"/>
+      <c r="J116" s="232"/>
+      <c r="K116" s="232"/>
+      <c r="L116" s="233"/>
       <c r="M116" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N116" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O116" s="140">
         <v>46177</v>
@@ -13940,7 +13940,7 @@
         <v>247</v>
       </c>
       <c r="R116" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S116" s="72">
         <v>46188</v>
@@ -13952,7 +13952,7 @@
         <v>45</v>
       </c>
       <c r="V116" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W116" s="130">
         <v>46196</v>
@@ -14006,15 +14006,15 @@
       <c r="H117" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I117" s="194"/>
-      <c r="J117" s="195"/>
-      <c r="K117" s="195"/>
-      <c r="L117" s="196"/>
+      <c r="I117" s="231"/>
+      <c r="J117" s="232"/>
+      <c r="K117" s="232"/>
+      <c r="L117" s="233"/>
       <c r="M117" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N117" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O117" s="140">
         <v>46177</v>
@@ -14026,7 +14026,7 @@
         <v>247</v>
       </c>
       <c r="R117" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S117" s="72">
         <v>46188</v>
@@ -14038,7 +14038,7 @@
         <v>45</v>
       </c>
       <c r="V117" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W117" s="130">
         <v>46196</v>
@@ -14092,15 +14092,15 @@
       <c r="H118" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I118" s="194"/>
-      <c r="J118" s="195"/>
-      <c r="K118" s="195"/>
-      <c r="L118" s="196"/>
+      <c r="I118" s="231"/>
+      <c r="J118" s="232"/>
+      <c r="K118" s="232"/>
+      <c r="L118" s="233"/>
       <c r="M118" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N118" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O118" s="140">
         <v>46177</v>
@@ -14112,7 +14112,7 @@
         <v>247</v>
       </c>
       <c r="R118" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S118" s="72">
         <v>46188</v>
@@ -14124,7 +14124,7 @@
         <v>45</v>
       </c>
       <c r="V118" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W118" s="130">
         <v>46196</v>
@@ -14178,15 +14178,15 @@
       <c r="H119" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I119" s="194"/>
-      <c r="J119" s="195"/>
-      <c r="K119" s="195"/>
-      <c r="L119" s="196"/>
+      <c r="I119" s="231"/>
+      <c r="J119" s="232"/>
+      <c r="K119" s="232"/>
+      <c r="L119" s="233"/>
       <c r="M119" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N119" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O119" s="140">
         <v>46169</v>
@@ -14198,7 +14198,7 @@
         <v>247</v>
       </c>
       <c r="R119" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S119" s="72">
         <v>46181</v>
@@ -14210,7 +14210,7 @@
         <v>45</v>
       </c>
       <c r="V119" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W119" s="130">
         <v>46195</v>
@@ -14264,15 +14264,15 @@
       <c r="H120" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I120" s="194"/>
-      <c r="J120" s="195"/>
-      <c r="K120" s="195"/>
-      <c r="L120" s="196"/>
+      <c r="I120" s="231"/>
+      <c r="J120" s="232"/>
+      <c r="K120" s="232"/>
+      <c r="L120" s="233"/>
       <c r="M120" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N120" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O120" s="140">
         <v>46169</v>
@@ -14284,7 +14284,7 @@
         <v>247</v>
       </c>
       <c r="R120" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S120" s="72">
         <v>46181</v>
@@ -14296,7 +14296,7 @@
         <v>45</v>
       </c>
       <c r="V120" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W120" s="130">
         <v>46195</v>
@@ -14350,15 +14350,15 @@
       <c r="H121" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I121" s="194"/>
-      <c r="J121" s="195"/>
-      <c r="K121" s="195"/>
-      <c r="L121" s="196"/>
+      <c r="I121" s="231"/>
+      <c r="J121" s="232"/>
+      <c r="K121" s="232"/>
+      <c r="L121" s="233"/>
       <c r="M121" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N121" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" s="140">
         <v>46169</v>
@@ -14370,7 +14370,7 @@
         <v>247</v>
       </c>
       <c r="R121" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S121" s="72">
         <v>46181</v>
@@ -14382,7 +14382,7 @@
         <v>45</v>
       </c>
       <c r="V121" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W121" s="130">
         <v>46195</v>
@@ -14436,15 +14436,15 @@
       <c r="H122" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I122" s="194"/>
-      <c r="J122" s="195"/>
-      <c r="K122" s="195"/>
-      <c r="L122" s="196"/>
+      <c r="I122" s="231"/>
+      <c r="J122" s="232"/>
+      <c r="K122" s="232"/>
+      <c r="L122" s="233"/>
       <c r="M122" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N122" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O122" s="140">
         <v>46169</v>
@@ -14456,7 +14456,7 @@
         <v>247</v>
       </c>
       <c r="R122" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S122" s="72">
         <v>46181</v>
@@ -14468,7 +14468,7 @@
         <v>45</v>
       </c>
       <c r="V122" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" s="130">
         <v>46195</v>
@@ -14522,15 +14522,15 @@
       <c r="H123" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I123" s="194"/>
-      <c r="J123" s="195"/>
-      <c r="K123" s="195"/>
-      <c r="L123" s="196"/>
+      <c r="I123" s="231"/>
+      <c r="J123" s="232"/>
+      <c r="K123" s="232"/>
+      <c r="L123" s="233"/>
       <c r="M123" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N123" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O123" s="140">
         <v>46169</v>
@@ -14542,7 +14542,7 @@
         <v>247</v>
       </c>
       <c r="R123" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S123" s="72">
         <v>46181</v>
@@ -14554,7 +14554,7 @@
         <v>45</v>
       </c>
       <c r="V123" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W123" s="130">
         <v>46195</v>
@@ -14608,15 +14608,15 @@
       <c r="H124" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I124" s="194"/>
-      <c r="J124" s="195"/>
-      <c r="K124" s="195"/>
-      <c r="L124" s="196"/>
+      <c r="I124" s="231"/>
+      <c r="J124" s="232"/>
+      <c r="K124" s="232"/>
+      <c r="L124" s="233"/>
       <c r="M124" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N124" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O124" s="140">
         <v>46169</v>
@@ -14628,7 +14628,7 @@
         <v>247</v>
       </c>
       <c r="R124" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S124" s="72">
         <v>46181</v>
@@ -14640,7 +14640,7 @@
         <v>45</v>
       </c>
       <c r="V124" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" s="130">
         <v>46195</v>
@@ -14694,15 +14694,15 @@
       <c r="H125" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I125" s="194"/>
-      <c r="J125" s="195"/>
-      <c r="K125" s="195"/>
-      <c r="L125" s="196"/>
+      <c r="I125" s="231"/>
+      <c r="J125" s="232"/>
+      <c r="K125" s="232"/>
+      <c r="L125" s="233"/>
       <c r="M125" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N125" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O125" s="140">
         <v>46169</v>
@@ -14714,7 +14714,7 @@
         <v>247</v>
       </c>
       <c r="R125" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S125" s="72">
         <v>46181</v>
@@ -14726,7 +14726,7 @@
         <v>45</v>
       </c>
       <c r="V125" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W125" s="130">
         <v>46195</v>
@@ -14780,15 +14780,15 @@
       <c r="H126" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I126" s="194"/>
-      <c r="J126" s="195"/>
-      <c r="K126" s="195"/>
-      <c r="L126" s="196"/>
+      <c r="I126" s="231"/>
+      <c r="J126" s="232"/>
+      <c r="K126" s="232"/>
+      <c r="L126" s="233"/>
       <c r="M126" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N126" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O126" s="140">
         <v>46169</v>
@@ -14800,7 +14800,7 @@
         <v>247</v>
       </c>
       <c r="R126" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S126" s="72">
         <v>46181</v>
@@ -14812,7 +14812,7 @@
         <v>45</v>
       </c>
       <c r="V126" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W126" s="130">
         <v>46195</v>
@@ -14866,15 +14866,15 @@
       <c r="H127" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I127" s="194"/>
-      <c r="J127" s="195"/>
-      <c r="K127" s="195"/>
-      <c r="L127" s="196"/>
+      <c r="I127" s="231"/>
+      <c r="J127" s="232"/>
+      <c r="K127" s="232"/>
+      <c r="L127" s="233"/>
       <c r="M127" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N127" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O127" s="140">
         <v>46169</v>
@@ -14886,7 +14886,7 @@
         <v>247</v>
       </c>
       <c r="R127" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S127" s="72">
         <v>46181</v>
@@ -14898,7 +14898,7 @@
         <v>45</v>
       </c>
       <c r="V127" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" s="130">
         <v>46195</v>
@@ -14950,15 +14950,15 @@
       <c r="H128" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I128" s="194"/>
-      <c r="J128" s="195"/>
-      <c r="K128" s="195"/>
-      <c r="L128" s="196"/>
+      <c r="I128" s="231"/>
+      <c r="J128" s="232"/>
+      <c r="K128" s="232"/>
+      <c r="L128" s="233"/>
       <c r="M128" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N128" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O128" s="140">
         <v>46169</v>
@@ -14970,7 +14970,7 @@
         <v>247</v>
       </c>
       <c r="R128" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S128" s="72">
         <v>46181</v>
@@ -14982,7 +14982,7 @@
         <v>45</v>
       </c>
       <c r="V128" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W128" s="130">
         <v>46195</v>
@@ -15036,15 +15036,15 @@
       <c r="H129" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I129" s="194"/>
-      <c r="J129" s="195"/>
-      <c r="K129" s="195"/>
-      <c r="L129" s="196"/>
+      <c r="I129" s="231"/>
+      <c r="J129" s="232"/>
+      <c r="K129" s="232"/>
+      <c r="L129" s="233"/>
       <c r="M129" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N129" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O129" s="140">
         <v>46169</v>
@@ -15056,7 +15056,7 @@
         <v>247</v>
       </c>
       <c r="R129" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S129" s="72">
         <v>46181</v>
@@ -15068,7 +15068,7 @@
         <v>45</v>
       </c>
       <c r="V129" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W129" s="130">
         <v>46195</v>
@@ -15122,15 +15122,15 @@
       <c r="H130" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I130" s="194"/>
-      <c r="J130" s="195"/>
-      <c r="K130" s="195"/>
-      <c r="L130" s="196"/>
+      <c r="I130" s="231"/>
+      <c r="J130" s="232"/>
+      <c r="K130" s="232"/>
+      <c r="L130" s="233"/>
       <c r="M130" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N130" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O130" s="140">
         <v>46169</v>
@@ -15142,7 +15142,7 @@
         <v>247</v>
       </c>
       <c r="R130" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S130" s="72">
         <v>46181</v>
@@ -15154,7 +15154,7 @@
         <v>45</v>
       </c>
       <c r="V130" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W130" s="130">
         <v>46195</v>
@@ -15208,15 +15208,15 @@
       <c r="H131" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I131" s="194"/>
-      <c r="J131" s="195"/>
-      <c r="K131" s="195"/>
-      <c r="L131" s="196"/>
+      <c r="I131" s="231"/>
+      <c r="J131" s="232"/>
+      <c r="K131" s="232"/>
+      <c r="L131" s="233"/>
       <c r="M131" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N131" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O131" s="140">
         <v>46169</v>
@@ -15228,7 +15228,7 @@
         <v>247</v>
       </c>
       <c r="R131" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S131" s="72">
         <v>46181</v>
@@ -15240,7 +15240,7 @@
         <v>45</v>
       </c>
       <c r="V131" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W131" s="130">
         <v>46195</v>
@@ -15294,15 +15294,15 @@
       <c r="H132" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I132" s="194"/>
-      <c r="J132" s="195"/>
-      <c r="K132" s="195"/>
-      <c r="L132" s="196"/>
+      <c r="I132" s="231"/>
+      <c r="J132" s="232"/>
+      <c r="K132" s="232"/>
+      <c r="L132" s="233"/>
       <c r="M132" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N132" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O132" s="140">
         <v>46169</v>
@@ -15314,7 +15314,7 @@
         <v>247</v>
       </c>
       <c r="R132" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S132" s="72">
         <v>46181</v>
@@ -15326,7 +15326,7 @@
         <v>45</v>
       </c>
       <c r="V132" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W132" s="130">
         <v>46195</v>
@@ -15380,15 +15380,15 @@
       <c r="H133" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I133" s="194"/>
-      <c r="J133" s="195"/>
-      <c r="K133" s="195"/>
-      <c r="L133" s="196"/>
+      <c r="I133" s="231"/>
+      <c r="J133" s="232"/>
+      <c r="K133" s="232"/>
+      <c r="L133" s="233"/>
       <c r="M133" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N133" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O133" s="140">
         <v>46169</v>
@@ -15400,7 +15400,7 @@
         <v>247</v>
       </c>
       <c r="R133" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S133" s="72">
         <v>46181</v>
@@ -15412,7 +15412,7 @@
         <v>45</v>
       </c>
       <c r="V133" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W133" s="130">
         <v>46195</v>
@@ -15466,15 +15466,15 @@
       <c r="H134" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I134" s="194"/>
-      <c r="J134" s="195"/>
-      <c r="K134" s="195"/>
-      <c r="L134" s="196"/>
+      <c r="I134" s="231"/>
+      <c r="J134" s="232"/>
+      <c r="K134" s="232"/>
+      <c r="L134" s="233"/>
       <c r="M134" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N134" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O134" s="140">
         <v>46169</v>
@@ -15486,7 +15486,7 @@
         <v>247</v>
       </c>
       <c r="R134" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S134" s="72">
         <v>46181</v>
@@ -15498,7 +15498,7 @@
         <v>45</v>
       </c>
       <c r="V134" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W134" s="130">
         <v>46195</v>
@@ -15552,15 +15552,15 @@
       <c r="H135" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I135" s="194"/>
-      <c r="J135" s="195"/>
-      <c r="K135" s="195"/>
-      <c r="L135" s="196"/>
+      <c r="I135" s="231"/>
+      <c r="J135" s="232"/>
+      <c r="K135" s="232"/>
+      <c r="L135" s="233"/>
       <c r="M135" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N135" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O135" s="140">
         <v>46169</v>
@@ -15572,7 +15572,7 @@
         <v>247</v>
       </c>
       <c r="R135" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S135" s="72">
         <v>46181</v>
@@ -15584,7 +15584,7 @@
         <v>45</v>
       </c>
       <c r="V135" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W135" s="130">
         <v>46195</v>
@@ -15638,17 +15638,17 @@
       <c r="H136" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I136" s="194" t="s">
+      <c r="I136" s="231" t="s">
         <v>245</v>
       </c>
-      <c r="J136" s="195"/>
-      <c r="K136" s="195"/>
-      <c r="L136" s="196"/>
+      <c r="J136" s="232"/>
+      <c r="K136" s="232"/>
+      <c r="L136" s="233"/>
       <c r="M136" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N136" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O136" s="140">
         <v>46169</v>
@@ -15660,7 +15660,7 @@
         <v>247</v>
       </c>
       <c r="R136" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S136" s="72">
         <v>46181</v>
@@ -15672,7 +15672,7 @@
         <v>45</v>
       </c>
       <c r="V136" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W136" s="130">
         <v>46195</v>
@@ -15726,15 +15726,15 @@
       <c r="H137" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I137" s="194"/>
-      <c r="J137" s="195"/>
-      <c r="K137" s="195"/>
-      <c r="L137" s="196"/>
+      <c r="I137" s="231"/>
+      <c r="J137" s="232"/>
+      <c r="K137" s="232"/>
+      <c r="L137" s="233"/>
       <c r="M137" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N137" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O137" s="140">
         <v>46169</v>
@@ -15746,7 +15746,7 @@
         <v>247</v>
       </c>
       <c r="R137" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S137" s="72">
         <v>46181</v>
@@ -15758,7 +15758,7 @@
         <v>45</v>
       </c>
       <c r="V137" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W137" s="130">
         <v>46195</v>
@@ -15812,15 +15812,15 @@
       <c r="H138" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I138" s="194"/>
-      <c r="J138" s="195"/>
-      <c r="K138" s="195"/>
-      <c r="L138" s="196"/>
+      <c r="I138" s="231"/>
+      <c r="J138" s="232"/>
+      <c r="K138" s="232"/>
+      <c r="L138" s="233"/>
       <c r="M138" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N138" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O138" s="140">
         <v>46169</v>
@@ -15832,7 +15832,7 @@
         <v>247</v>
       </c>
       <c r="R138" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S138" s="72">
         <v>46181</v>
@@ -15844,7 +15844,7 @@
         <v>45</v>
       </c>
       <c r="V138" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W138" s="130">
         <v>46195</v>
@@ -15898,15 +15898,15 @@
       <c r="H139" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I139" s="194"/>
-      <c r="J139" s="195"/>
-      <c r="K139" s="195"/>
-      <c r="L139" s="196"/>
+      <c r="I139" s="231"/>
+      <c r="J139" s="232"/>
+      <c r="K139" s="232"/>
+      <c r="L139" s="233"/>
       <c r="M139" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N139" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O139" s="140">
         <v>46169</v>
@@ -15918,7 +15918,7 @@
         <v>247</v>
       </c>
       <c r="R139" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S139" s="72">
         <v>46181</v>
@@ -15930,7 +15930,7 @@
         <v>45</v>
       </c>
       <c r="V139" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" s="130">
         <v>46195</v>
@@ -15984,15 +15984,15 @@
       <c r="H140" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I140" s="194"/>
-      <c r="J140" s="195"/>
-      <c r="K140" s="195"/>
-      <c r="L140" s="196"/>
+      <c r="I140" s="231"/>
+      <c r="J140" s="232"/>
+      <c r="K140" s="232"/>
+      <c r="L140" s="233"/>
       <c r="M140" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N140" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O140" s="140">
         <v>46169</v>
@@ -16004,7 +16004,7 @@
         <v>247</v>
       </c>
       <c r="R140" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S140" s="72">
         <v>46181</v>
@@ -16016,7 +16016,7 @@
         <v>45</v>
       </c>
       <c r="V140" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W140" s="130">
         <v>46195</v>
@@ -16070,15 +16070,15 @@
       <c r="H141" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I141" s="194"/>
-      <c r="J141" s="195"/>
-      <c r="K141" s="195"/>
-      <c r="L141" s="196"/>
+      <c r="I141" s="231"/>
+      <c r="J141" s="232"/>
+      <c r="K141" s="232"/>
+      <c r="L141" s="233"/>
       <c r="M141" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N141" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O141" s="140">
         <v>46169</v>
@@ -16090,7 +16090,7 @@
         <v>247</v>
       </c>
       <c r="R141" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S141" s="72">
         <v>46181</v>
@@ -16102,7 +16102,7 @@
         <v>45</v>
       </c>
       <c r="V141" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W141" s="130">
         <v>46195</v>
@@ -16154,15 +16154,15 @@
       <c r="H142" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I142" s="194"/>
-      <c r="J142" s="195"/>
-      <c r="K142" s="195"/>
-      <c r="L142" s="196"/>
+      <c r="I142" s="231"/>
+      <c r="J142" s="232"/>
+      <c r="K142" s="232"/>
+      <c r="L142" s="233"/>
       <c r="M142" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N142" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O142" s="140">
         <v>46169</v>
@@ -16174,7 +16174,7 @@
         <v>247</v>
       </c>
       <c r="R142" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S142" s="72">
         <v>46181</v>
@@ -16186,7 +16186,7 @@
         <v>45</v>
       </c>
       <c r="V142" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" s="130">
         <v>46195</v>
@@ -16240,15 +16240,15 @@
       <c r="H143" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I143" s="194"/>
-      <c r="J143" s="195"/>
-      <c r="K143" s="195"/>
-      <c r="L143" s="196"/>
+      <c r="I143" s="231"/>
+      <c r="J143" s="232"/>
+      <c r="K143" s="232"/>
+      <c r="L143" s="233"/>
       <c r="M143" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N143" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O143" s="140">
         <v>46169</v>
@@ -16260,7 +16260,7 @@
         <v>247</v>
       </c>
       <c r="R143" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S143" s="72">
         <v>46181</v>
@@ -16272,7 +16272,7 @@
         <v>45</v>
       </c>
       <c r="V143" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W143" s="130">
         <v>46195</v>
@@ -16324,17 +16324,17 @@
       <c r="H144" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I144" s="194" t="s">
+      <c r="I144" s="231" t="s">
         <v>246</v>
       </c>
-      <c r="J144" s="195"/>
-      <c r="K144" s="195"/>
-      <c r="L144" s="196"/>
+      <c r="J144" s="232"/>
+      <c r="K144" s="232"/>
+      <c r="L144" s="233"/>
       <c r="M144" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N144" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O144" s="140">
         <v>46169</v>
@@ -16346,7 +16346,7 @@
         <v>247</v>
       </c>
       <c r="R144" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S144" s="72">
         <v>46181</v>
@@ -16358,7 +16358,7 @@
         <v>45</v>
       </c>
       <c r="V144" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W144" s="130">
         <v>46195</v>
@@ -16412,15 +16412,15 @@
       <c r="H145" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I145" s="194"/>
-      <c r="J145" s="195"/>
-      <c r="K145" s="195"/>
-      <c r="L145" s="196"/>
+      <c r="I145" s="231"/>
+      <c r="J145" s="232"/>
+      <c r="K145" s="232"/>
+      <c r="L145" s="233"/>
       <c r="M145" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N145" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O145" s="140">
         <v>46169</v>
@@ -16432,7 +16432,7 @@
         <v>247</v>
       </c>
       <c r="R145" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S145" s="72">
         <v>46181</v>
@@ -16444,7 +16444,7 @@
         <v>45</v>
       </c>
       <c r="V145" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W145" s="130">
         <v>46195</v>
@@ -16498,15 +16498,15 @@
       <c r="H146" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I146" s="194"/>
-      <c r="J146" s="195"/>
-      <c r="K146" s="195"/>
-      <c r="L146" s="196"/>
+      <c r="I146" s="231"/>
+      <c r="J146" s="232"/>
+      <c r="K146" s="232"/>
+      <c r="L146" s="233"/>
       <c r="M146" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N146" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O146" s="140">
         <v>46169</v>
@@ -16518,7 +16518,7 @@
         <v>247</v>
       </c>
       <c r="R146" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S146" s="72">
         <v>46181</v>
@@ -16530,7 +16530,7 @@
         <v>45</v>
       </c>
       <c r="V146" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W146" s="130">
         <v>46195</v>
@@ -16584,15 +16584,15 @@
       <c r="H147" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I147" s="194"/>
-      <c r="J147" s="195"/>
-      <c r="K147" s="195"/>
-      <c r="L147" s="196"/>
+      <c r="I147" s="231"/>
+      <c r="J147" s="232"/>
+      <c r="K147" s="232"/>
+      <c r="L147" s="233"/>
       <c r="M147" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N147" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O147" s="140">
         <v>46169</v>
@@ -16604,7 +16604,7 @@
         <v>247</v>
       </c>
       <c r="R147" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S147" s="72">
         <v>46181</v>
@@ -16616,7 +16616,7 @@
         <v>45</v>
       </c>
       <c r="V147" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W147" s="130">
         <v>46195</v>
@@ -16670,15 +16670,15 @@
       <c r="H148" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I148" s="194"/>
-      <c r="J148" s="195"/>
-      <c r="K148" s="195"/>
-      <c r="L148" s="196"/>
+      <c r="I148" s="231"/>
+      <c r="J148" s="232"/>
+      <c r="K148" s="232"/>
+      <c r="L148" s="233"/>
       <c r="M148" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N148" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O148" s="140">
         <v>46169</v>
@@ -16690,7 +16690,7 @@
         <v>247</v>
       </c>
       <c r="R148" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S148" s="72">
         <v>46181</v>
@@ -16702,7 +16702,7 @@
         <v>45</v>
       </c>
       <c r="V148" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W148" s="130">
         <v>46195</v>
@@ -16754,15 +16754,15 @@
       <c r="H149" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I149" s="194"/>
-      <c r="J149" s="195"/>
-      <c r="K149" s="195"/>
-      <c r="L149" s="196"/>
+      <c r="I149" s="231"/>
+      <c r="J149" s="232"/>
+      <c r="K149" s="232"/>
+      <c r="L149" s="233"/>
       <c r="M149" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N149" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O149" s="140">
         <v>46169</v>
@@ -16774,7 +16774,7 @@
         <v>247</v>
       </c>
       <c r="R149" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S149" s="72">
         <v>46181</v>
@@ -16786,7 +16786,7 @@
         <v>45</v>
       </c>
       <c r="V149" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W149" s="130">
         <v>46195</v>
@@ -16838,15 +16838,15 @@
       <c r="H150" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I150" s="194"/>
-      <c r="J150" s="195"/>
-      <c r="K150" s="195"/>
-      <c r="L150" s="196"/>
+      <c r="I150" s="231"/>
+      <c r="J150" s="232"/>
+      <c r="K150" s="232"/>
+      <c r="L150" s="233"/>
       <c r="M150" s="84" t="s">
         <v>45</v>
       </c>
       <c r="N150" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O150" s="140">
         <v>46169</v>
@@ -16858,7 +16858,7 @@
         <v>247</v>
       </c>
       <c r="R150" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S150" s="72">
         <v>46181</v>
@@ -16870,7 +16870,7 @@
         <v>45</v>
       </c>
       <c r="V150" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W150" s="130">
         <v>46195</v>
@@ -16909,7 +16909,7 @@
     </row>
     <row r="151" spans="1:52" ht="15" customHeight="1">
       <c r="A151" s="9"/>
-      <c r="B151" s="254" t="s">
+      <c r="B151" s="194" t="s">
         <v>225</v>
       </c>
       <c r="C151" s="153" t="s">
@@ -16922,10 +16922,10 @@
       <c r="H151" s="155" t="s">
         <v>44</v>
       </c>
-      <c r="I151" s="194"/>
-      <c r="J151" s="195"/>
-      <c r="K151" s="195"/>
-      <c r="L151" s="196"/>
+      <c r="I151" s="231"/>
+      <c r="J151" s="232"/>
+      <c r="K151" s="232"/>
+      <c r="L151" s="233"/>
       <c r="M151" s="84"/>
       <c r="N151" s="67"/>
       <c r="O151" s="140"/>
@@ -16938,7 +16938,7 @@
         <v>45</v>
       </c>
       <c r="V151" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W151" s="130">
         <v>46198</v>
@@ -16977,7 +16977,7 @@
     </row>
     <row r="152" spans="1:52" ht="15" customHeight="1">
       <c r="A152" s="9"/>
-      <c r="B152" s="254" t="s">
+      <c r="B152" s="194" t="s">
         <v>227</v>
       </c>
       <c r="C152" s="125" t="s">
@@ -16990,10 +16990,10 @@
       <c r="H152" s="129" t="s">
         <v>44</v>
       </c>
-      <c r="I152" s="194"/>
-      <c r="J152" s="195"/>
-      <c r="K152" s="195"/>
-      <c r="L152" s="196"/>
+      <c r="I152" s="231"/>
+      <c r="J152" s="232"/>
+      <c r="K152" s="232"/>
+      <c r="L152" s="233"/>
       <c r="M152" s="84"/>
       <c r="N152" s="67"/>
       <c r="O152" s="140"/>
@@ -17052,10 +17052,10 @@
       <c r="F153" s="145"/>
       <c r="G153" s="145"/>
       <c r="H153" s="146"/>
-      <c r="I153" s="197"/>
-      <c r="J153" s="198"/>
-      <c r="K153" s="198"/>
-      <c r="L153" s="199"/>
+      <c r="I153" s="252"/>
+      <c r="J153" s="253"/>
+      <c r="K153" s="253"/>
+      <c r="L153" s="254"/>
       <c r="M153" s="147"/>
       <c r="N153" s="77"/>
       <c r="O153" s="148"/>
@@ -66131,6 +66131,164 @@
     </row>
   </sheetData>
   <mergeCells count="177">
+    <mergeCell ref="I150:L150"/>
+    <mergeCell ref="I151:L151"/>
+    <mergeCell ref="I152:L152"/>
+    <mergeCell ref="I153:L153"/>
+    <mergeCell ref="I145:L145"/>
+    <mergeCell ref="I146:L146"/>
+    <mergeCell ref="I147:L147"/>
+    <mergeCell ref="I148:L148"/>
+    <mergeCell ref="I149:L149"/>
+    <mergeCell ref="I140:L140"/>
+    <mergeCell ref="I141:L141"/>
+    <mergeCell ref="I142:L142"/>
+    <mergeCell ref="I143:L143"/>
+    <mergeCell ref="I144:L144"/>
+    <mergeCell ref="I135:L135"/>
+    <mergeCell ref="I136:L136"/>
+    <mergeCell ref="I137:L137"/>
+    <mergeCell ref="I138:L138"/>
+    <mergeCell ref="I139:L139"/>
+    <mergeCell ref="I130:L130"/>
+    <mergeCell ref="I131:L131"/>
+    <mergeCell ref="I132:L132"/>
+    <mergeCell ref="I133:L133"/>
+    <mergeCell ref="I134:L134"/>
+    <mergeCell ref="I125:L125"/>
+    <mergeCell ref="I126:L126"/>
+    <mergeCell ref="I127:L127"/>
+    <mergeCell ref="I128:L128"/>
+    <mergeCell ref="I129:L129"/>
+    <mergeCell ref="I120:L120"/>
+    <mergeCell ref="I121:L121"/>
+    <mergeCell ref="I122:L122"/>
+    <mergeCell ref="I123:L123"/>
+    <mergeCell ref="I124:L124"/>
+    <mergeCell ref="I115:L115"/>
+    <mergeCell ref="I116:L116"/>
+    <mergeCell ref="I117:L117"/>
+    <mergeCell ref="I118:L118"/>
+    <mergeCell ref="I119:L119"/>
+    <mergeCell ref="I110:L110"/>
+    <mergeCell ref="I111:L111"/>
+    <mergeCell ref="I112:L112"/>
+    <mergeCell ref="I113:L113"/>
+    <mergeCell ref="I114:L114"/>
+    <mergeCell ref="I105:L105"/>
+    <mergeCell ref="I106:L106"/>
+    <mergeCell ref="I107:L107"/>
+    <mergeCell ref="I108:L108"/>
+    <mergeCell ref="I109:L109"/>
+    <mergeCell ref="I100:L100"/>
+    <mergeCell ref="I101:L101"/>
+    <mergeCell ref="I102:L102"/>
+    <mergeCell ref="I103:L103"/>
+    <mergeCell ref="I104:L104"/>
+    <mergeCell ref="I95:L95"/>
+    <mergeCell ref="I96:L96"/>
+    <mergeCell ref="I97:L97"/>
+    <mergeCell ref="I98:L98"/>
+    <mergeCell ref="I99:L99"/>
+    <mergeCell ref="I90:L90"/>
+    <mergeCell ref="I91:L91"/>
+    <mergeCell ref="I92:L92"/>
+    <mergeCell ref="I93:L93"/>
+    <mergeCell ref="I94:L94"/>
+    <mergeCell ref="I85:L85"/>
+    <mergeCell ref="I86:L86"/>
+    <mergeCell ref="I87:L87"/>
+    <mergeCell ref="I88:L88"/>
+    <mergeCell ref="I89:L89"/>
+    <mergeCell ref="I80:L80"/>
+    <mergeCell ref="I81:L81"/>
+    <mergeCell ref="I82:L82"/>
+    <mergeCell ref="I83:L83"/>
+    <mergeCell ref="I84:L84"/>
+    <mergeCell ref="I75:L75"/>
+    <mergeCell ref="I76:L76"/>
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="I78:L78"/>
+    <mergeCell ref="I79:L79"/>
+    <mergeCell ref="I70:L70"/>
+    <mergeCell ref="I71:L71"/>
+    <mergeCell ref="I72:L72"/>
+    <mergeCell ref="I73:L73"/>
+    <mergeCell ref="I74:L74"/>
+    <mergeCell ref="I65:L65"/>
+    <mergeCell ref="I66:L66"/>
+    <mergeCell ref="I67:L67"/>
+    <mergeCell ref="I68:L68"/>
+    <mergeCell ref="I69:L69"/>
+    <mergeCell ref="I60:L60"/>
+    <mergeCell ref="I61:L61"/>
+    <mergeCell ref="I62:L62"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="I64:L64"/>
+    <mergeCell ref="I55:L55"/>
+    <mergeCell ref="I56:L56"/>
+    <mergeCell ref="I57:L57"/>
+    <mergeCell ref="I58:L58"/>
+    <mergeCell ref="I59:L59"/>
+    <mergeCell ref="I50:L50"/>
+    <mergeCell ref="I51:L51"/>
+    <mergeCell ref="I52:L52"/>
+    <mergeCell ref="I53:L53"/>
+    <mergeCell ref="I54:L54"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="Q5:T5"/>
+    <mergeCell ref="H3:H6"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="B2:F4"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="Q8:T8"/>
+    <mergeCell ref="C8:C9"/>
     <mergeCell ref="AJ8:AN8"/>
     <mergeCell ref="M4:P4"/>
     <mergeCell ref="I8:L9"/>
@@ -66150,164 +66308,6 @@
     <mergeCell ref="U6:X6"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="G8:G9"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="Q5:T5"/>
-    <mergeCell ref="H3:H6"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="Q6:T6"/>
-    <mergeCell ref="B2:F4"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="Q8:T8"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="I51:L51"/>
-    <mergeCell ref="I52:L52"/>
-    <mergeCell ref="I53:L53"/>
-    <mergeCell ref="I54:L54"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="I60:L60"/>
-    <mergeCell ref="I61:L61"/>
-    <mergeCell ref="I62:L62"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="I64:L64"/>
-    <mergeCell ref="I55:L55"/>
-    <mergeCell ref="I56:L56"/>
-    <mergeCell ref="I57:L57"/>
-    <mergeCell ref="I58:L58"/>
-    <mergeCell ref="I59:L59"/>
-    <mergeCell ref="I70:L70"/>
-    <mergeCell ref="I71:L71"/>
-    <mergeCell ref="I72:L72"/>
-    <mergeCell ref="I73:L73"/>
-    <mergeCell ref="I74:L74"/>
-    <mergeCell ref="I65:L65"/>
-    <mergeCell ref="I66:L66"/>
-    <mergeCell ref="I67:L67"/>
-    <mergeCell ref="I68:L68"/>
-    <mergeCell ref="I69:L69"/>
-    <mergeCell ref="I80:L80"/>
-    <mergeCell ref="I81:L81"/>
-    <mergeCell ref="I82:L82"/>
-    <mergeCell ref="I83:L83"/>
-    <mergeCell ref="I84:L84"/>
-    <mergeCell ref="I75:L75"/>
-    <mergeCell ref="I76:L76"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="I78:L78"/>
-    <mergeCell ref="I79:L79"/>
-    <mergeCell ref="I90:L90"/>
-    <mergeCell ref="I91:L91"/>
-    <mergeCell ref="I92:L92"/>
-    <mergeCell ref="I93:L93"/>
-    <mergeCell ref="I94:L94"/>
-    <mergeCell ref="I85:L85"/>
-    <mergeCell ref="I86:L86"/>
-    <mergeCell ref="I87:L87"/>
-    <mergeCell ref="I88:L88"/>
-    <mergeCell ref="I89:L89"/>
-    <mergeCell ref="I100:L100"/>
-    <mergeCell ref="I101:L101"/>
-    <mergeCell ref="I102:L102"/>
-    <mergeCell ref="I103:L103"/>
-    <mergeCell ref="I104:L104"/>
-    <mergeCell ref="I95:L95"/>
-    <mergeCell ref="I96:L96"/>
-    <mergeCell ref="I97:L97"/>
-    <mergeCell ref="I98:L98"/>
-    <mergeCell ref="I99:L99"/>
-    <mergeCell ref="I110:L110"/>
-    <mergeCell ref="I111:L111"/>
-    <mergeCell ref="I112:L112"/>
-    <mergeCell ref="I113:L113"/>
-    <mergeCell ref="I114:L114"/>
-    <mergeCell ref="I105:L105"/>
-    <mergeCell ref="I106:L106"/>
-    <mergeCell ref="I107:L107"/>
-    <mergeCell ref="I108:L108"/>
-    <mergeCell ref="I109:L109"/>
-    <mergeCell ref="I120:L120"/>
-    <mergeCell ref="I121:L121"/>
-    <mergeCell ref="I122:L122"/>
-    <mergeCell ref="I123:L123"/>
-    <mergeCell ref="I124:L124"/>
-    <mergeCell ref="I115:L115"/>
-    <mergeCell ref="I116:L116"/>
-    <mergeCell ref="I117:L117"/>
-    <mergeCell ref="I118:L118"/>
-    <mergeCell ref="I119:L119"/>
-    <mergeCell ref="I130:L130"/>
-    <mergeCell ref="I131:L131"/>
-    <mergeCell ref="I132:L132"/>
-    <mergeCell ref="I133:L133"/>
-    <mergeCell ref="I134:L134"/>
-    <mergeCell ref="I125:L125"/>
-    <mergeCell ref="I126:L126"/>
-    <mergeCell ref="I127:L127"/>
-    <mergeCell ref="I128:L128"/>
-    <mergeCell ref="I129:L129"/>
-    <mergeCell ref="I140:L140"/>
-    <mergeCell ref="I141:L141"/>
-    <mergeCell ref="I142:L142"/>
-    <mergeCell ref="I143:L143"/>
-    <mergeCell ref="I144:L144"/>
-    <mergeCell ref="I135:L135"/>
-    <mergeCell ref="I136:L136"/>
-    <mergeCell ref="I137:L137"/>
-    <mergeCell ref="I138:L138"/>
-    <mergeCell ref="I139:L139"/>
-    <mergeCell ref="I150:L150"/>
-    <mergeCell ref="I151:L151"/>
-    <mergeCell ref="I152:L152"/>
-    <mergeCell ref="I153:L153"/>
-    <mergeCell ref="I145:L145"/>
-    <mergeCell ref="I146:L146"/>
-    <mergeCell ref="I147:L147"/>
-    <mergeCell ref="I148:L148"/>
-    <mergeCell ref="I149:L149"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <conditionalFormatting sqref="I13:I153">
@@ -66321,7 +66321,7 @@
       <formula>"2차"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M10:M13 V10:V54 N10:N153 Q10:R153 M38:M153 U38:V153">
+  <conditionalFormatting sqref="M10:M13 M38:M153 U38:V153 N10:N153 Q10:R153 V10:V150">
     <cfRule type="cellIs" dxfId="41" priority="26" operator="equal">
       <formula>"100%"</formula>
     </cfRule>
@@ -66331,7 +66331,7 @@
       <formula>"100%"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M29:M33 V10:V153 M40:M153 Q149:R153">
+  <conditionalFormatting sqref="M29:M33 M40:M153 Q149:R153 V10:V153">
     <cfRule type="cellIs" dxfId="39" priority="45" operator="equal">
       <formula>"0%"</formula>
     </cfRule>
@@ -66378,7 +66378,7 @@
       <formula>"0%"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N11:N153 M38:M153 U39:V153">
+  <conditionalFormatting sqref="M38:M153 U39:V153 N11:N153">
     <cfRule type="cellIs" dxfId="28" priority="61" operator="lessThan">
       <formula>"100%"</formula>
     </cfRule>
@@ -66391,12 +66391,12 @@
       <formula>"0%"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q10:R153 V10:V153 M29:M33 M40:M153">
+  <conditionalFormatting sqref="M29:M33 M40:M153 Q10:R153 V10:V153">
     <cfRule type="cellIs" dxfId="25" priority="46" operator="lessThan">
       <formula>"100%"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R10:R148 M10:N10 U10:U16 Q10:Q150 M11:M16 M18 U18:U19 U21:U25 M26:M28 U27:U34 M30:M32 M34 M36:M37 U40:U54">
+  <conditionalFormatting sqref="M10:N10 U10:U16 M11:M16 M18 U18:U19 U21:U25 M26:M28 U27:U34 M30:M32 M34 M36:M37 U40:U54 Q10:R150">
     <cfRule type="cellIs" dxfId="24" priority="21" operator="equal">
       <formula>"0%"</formula>
     </cfRule>
